--- a/research/traditional_assets/database/data/oman/oman_household_products.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09771427617851974</v>
+        <v>0.09760595476425196</v>
       </c>
       <c r="C2">
-        <v>48.83731136761881</v>
+        <v>48.43854626979243</v>
       </c>
       <c r="D2">
-        <v>46.81731136761881</v>
+        <v>46.89054626979243</v>
       </c>
       <c r="E2">
-        <v>-10.3</v>
+        <v>-9.828000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.472</v>
       </c>
       <c r="G2">
         <v>2.02</v>
@@ -1451,28 +1451,28 @@
         <v>4.95</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0237416</v>
       </c>
       <c r="N2">
-        <v>4.95</v>
+        <v>4.9262584</v>
       </c>
       <c r="O2">
-        <v>0.7425</v>
+        <v>0.73893876</v>
       </c>
       <c r="P2">
-        <v>4.2075</v>
+        <v>4.18731964</v>
       </c>
       <c r="Q2">
-        <v>5.9275</v>
+        <v>5.90731964</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09771427617851974</v>
+        <v>0.09816000481237572</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6824263892259379</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>208.4947939481754</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09760595476425196</v>
+        <v>0.09749763334998421</v>
       </c>
       <c r="C3">
-        <v>48.43854626979243</v>
+        <v>48.04001064920901</v>
       </c>
       <c r="D3">
-        <v>46.89054626979243</v>
+        <v>46.96401064920901</v>
       </c>
       <c r="E3">
-        <v>-9.828000000000001</v>
+        <v>-9.356</v>
       </c>
       <c r="F3">
-        <v>0.472</v>
+        <v>0.9440000000000001</v>
       </c>
       <c r="G3">
         <v>2.02</v>
@@ -1533,28 +1533,28 @@
         <v>4.95</v>
       </c>
       <c r="M3">
-        <v>0.0237416</v>
+        <v>0.0474832</v>
       </c>
       <c r="N3">
-        <v>4.9262584</v>
+        <v>4.9025168</v>
       </c>
       <c r="O3">
-        <v>0.73893876</v>
+        <v>0.73537752</v>
       </c>
       <c r="P3">
-        <v>4.18731964</v>
+        <v>4.16713928</v>
       </c>
       <c r="Q3">
-        <v>5.90731964</v>
+        <v>5.88713928</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09816000481237572</v>
+        <v>0.09861482994896348</v>
       </c>
       <c r="T3">
-        <v>0.6824263892259379</v>
+        <v>0.6883542854666466</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>208.4947939481754</v>
+        <v>104.2473969740877</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09749763334998421</v>
+        <v>0.0973893119357164</v>
       </c>
       <c r="C4">
-        <v>48.04001064920901</v>
+        <v>47.64170558614119</v>
       </c>
       <c r="D4">
-        <v>46.96401064920901</v>
+        <v>47.03770558614118</v>
       </c>
       <c r="E4">
-        <v>-9.356</v>
+        <v>-8.884</v>
       </c>
       <c r="F4">
-        <v>0.9440000000000001</v>
+        <v>1.416</v>
       </c>
       <c r="G4">
         <v>2.02</v>
@@ -1615,28 +1615,28 @@
         <v>4.95</v>
       </c>
       <c r="M4">
-        <v>0.0474832</v>
+        <v>0.07122479999999999</v>
       </c>
       <c r="N4">
-        <v>4.9025168</v>
+        <v>4.8787752</v>
       </c>
       <c r="O4">
-        <v>0.73537752</v>
+        <v>0.73181628</v>
       </c>
       <c r="P4">
-        <v>4.16713928</v>
+        <v>4.146958919999999</v>
       </c>
       <c r="Q4">
-        <v>5.88713928</v>
+        <v>5.866958919999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09861482994896348</v>
+        <v>0.09907903292341898</v>
       </c>
       <c r="T4">
-        <v>0.6883542854666466</v>
+        <v>0.6944044063721118</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.2473969740877</v>
+        <v>69.49826464939179</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0973893119357164</v>
+        <v>0.09728099052144863</v>
       </c>
       <c r="C5">
-        <v>47.64170558614119</v>
+        <v>47.24363216765267</v>
       </c>
       <c r="D5">
-        <v>47.03770558614118</v>
+        <v>47.11163216765267</v>
       </c>
       <c r="E5">
-        <v>-8.884</v>
+        <v>-8.412000000000001</v>
       </c>
       <c r="F5">
-        <v>1.416</v>
+        <v>1.888</v>
       </c>
       <c r="G5">
         <v>2.02</v>
@@ -1697,28 +1697,28 @@
         <v>4.95</v>
       </c>
       <c r="M5">
-        <v>0.07122479999999999</v>
+        <v>0.09496640000000001</v>
       </c>
       <c r="N5">
-        <v>4.8787752</v>
+        <v>4.855033600000001</v>
       </c>
       <c r="O5">
-        <v>0.73181628</v>
+        <v>0.7282550400000001</v>
       </c>
       <c r="P5">
-        <v>4.146958919999999</v>
+        <v>4.12677856</v>
       </c>
       <c r="Q5">
-        <v>5.866958919999999</v>
+        <v>5.84677856</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09907903292341898</v>
+        <v>0.09955290679317566</v>
       </c>
       <c r="T5">
-        <v>0.6944044063721118</v>
+        <v>0.7005805714631077</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.49826464939179</v>
+        <v>52.12369848704384</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09728099052144863</v>
+        <v>0.09717266910718084</v>
       </c>
       <c r="C6">
-        <v>47.24363216765267</v>
+        <v>46.84579148765201</v>
       </c>
       <c r="D6">
-        <v>47.11163216765267</v>
+        <v>47.185791487652</v>
       </c>
       <c r="E6">
-        <v>-8.412000000000001</v>
+        <v>-7.94</v>
       </c>
       <c r="F6">
-        <v>1.888</v>
+        <v>2.36</v>
       </c>
       <c r="G6">
         <v>2.02</v>
@@ -1779,28 +1779,28 @@
         <v>4.95</v>
       </c>
       <c r="M6">
-        <v>0.09496640000000001</v>
+        <v>0.118708</v>
       </c>
       <c r="N6">
-        <v>4.855033600000001</v>
+        <v>4.831292</v>
       </c>
       <c r="O6">
-        <v>0.7282550400000001</v>
+        <v>0.7246938000000001</v>
       </c>
       <c r="P6">
-        <v>4.12677856</v>
+        <v>4.106598200000001</v>
       </c>
       <c r="Q6">
-        <v>5.84677856</v>
+        <v>5.8265982</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09955290679317566</v>
+        <v>0.1000367569549272</v>
       </c>
       <c r="T6">
-        <v>0.7005805714631077</v>
+        <v>0.7068867610823351</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.12369848704384</v>
+        <v>41.69895878963507</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09717266910718084</v>
+        <v>0.09706434769291307</v>
       </c>
       <c r="C7">
-        <v>46.84579148765201</v>
+        <v>46.44818464694624</v>
       </c>
       <c r="D7">
-        <v>47.185791487652</v>
+        <v>47.26018464694624</v>
       </c>
       <c r="E7">
-        <v>-7.94</v>
+        <v>-7.468</v>
       </c>
       <c r="F7">
-        <v>2.36</v>
+        <v>2.832</v>
       </c>
       <c r="G7">
         <v>2.02</v>
@@ -1861,28 +1861,28 @@
         <v>4.95</v>
       </c>
       <c r="M7">
-        <v>0.118708</v>
+        <v>0.1424496</v>
       </c>
       <c r="N7">
-        <v>4.831292</v>
+        <v>4.8075504</v>
       </c>
       <c r="O7">
-        <v>0.7246938000000001</v>
+        <v>0.72113256</v>
       </c>
       <c r="P7">
-        <v>4.106598200000001</v>
+        <v>4.08641784</v>
       </c>
       <c r="Q7">
-        <v>5.8265982</v>
+        <v>5.80641784</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1000367569549272</v>
+        <v>0.1005309018009714</v>
       </c>
       <c r="T7">
-        <v>0.7068867610823351</v>
+        <v>0.71332712494878</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.69895878963507</v>
+        <v>34.74913232469589</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09706434769291306</v>
+        <v>0.0969560262786453</v>
       </c>
       <c r="C8">
-        <v>46.44818464694625</v>
+        <v>46.05081275329559</v>
       </c>
       <c r="D8">
-        <v>47.26018464694625</v>
+        <v>47.33481275329559</v>
       </c>
       <c r="E8">
-        <v>-7.468000000000001</v>
+        <v>-6.996</v>
       </c>
       <c r="F8">
-        <v>2.832</v>
+        <v>3.304</v>
       </c>
       <c r="G8">
         <v>2.02</v>
@@ -1943,28 +1943,28 @@
         <v>4.95</v>
       </c>
       <c r="M8">
-        <v>0.1424496</v>
+        <v>0.1661912</v>
       </c>
       <c r="N8">
-        <v>4.8075504</v>
+        <v>4.7838088</v>
       </c>
       <c r="O8">
-        <v>0.72113256</v>
+        <v>0.71757132</v>
       </c>
       <c r="P8">
-        <v>4.08641784</v>
+        <v>4.06623748</v>
       </c>
       <c r="Q8">
-        <v>5.80641784</v>
+        <v>5.78623748</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1005309018009714</v>
+        <v>0.1010356734178982</v>
       </c>
       <c r="T8">
-        <v>0.71332712494878</v>
+        <v>0.7199059912639658</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.7491323246959</v>
+        <v>29.78497056402506</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09695602627864529</v>
+        <v>0.09684770486437753</v>
       </c>
       <c r="C9">
-        <v>46.0508127532956</v>
+        <v>45.65367692146832</v>
       </c>
       <c r="D9">
-        <v>47.33481275329559</v>
+        <v>47.40967692146832</v>
       </c>
       <c r="E9">
-        <v>-6.996</v>
+        <v>-6.524000000000001</v>
       </c>
       <c r="F9">
-        <v>3.304000000000001</v>
+        <v>3.776</v>
       </c>
       <c r="G9">
         <v>2.02</v>
@@ -2025,28 +2025,28 @@
         <v>4.95</v>
       </c>
       <c r="M9">
-        <v>0.1661912</v>
+        <v>0.1899328</v>
       </c>
       <c r="N9">
-        <v>4.7838088</v>
+        <v>4.7600672</v>
       </c>
       <c r="O9">
-        <v>0.71757132</v>
+        <v>0.71401008</v>
       </c>
       <c r="P9">
-        <v>4.06623748</v>
+        <v>4.04605712</v>
       </c>
       <c r="Q9">
-        <v>5.78623748</v>
+        <v>5.76605712</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1010356734178982</v>
+        <v>0.1015514183308451</v>
       </c>
       <c r="T9">
-        <v>0.7199059912639658</v>
+        <v>0.7266278764120904</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.78497056402504</v>
+        <v>26.06184924352192</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09684770486437753</v>
+        <v>0.09673938345010973</v>
       </c>
       <c r="C10">
-        <v>45.65367692146832</v>
+        <v>45.25677827329636</v>
       </c>
       <c r="D10">
-        <v>47.40967692146832</v>
+        <v>47.48477827329635</v>
       </c>
       <c r="E10">
-        <v>-6.524000000000001</v>
+        <v>-6.052</v>
       </c>
       <c r="F10">
-        <v>3.776</v>
+        <v>4.248</v>
       </c>
       <c r="G10">
         <v>2.02</v>
@@ -2107,28 +2107,28 @@
         <v>4.95</v>
       </c>
       <c r="M10">
-        <v>0.1899328</v>
+        <v>0.2136744</v>
       </c>
       <c r="N10">
-        <v>4.7600672</v>
+        <v>4.7363256</v>
       </c>
       <c r="O10">
-        <v>0.71401008</v>
+        <v>0.71044884</v>
       </c>
       <c r="P10">
-        <v>4.04605712</v>
+        <v>4.02587676</v>
       </c>
       <c r="Q10">
-        <v>5.76605712</v>
+        <v>5.74587676</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1015514183308451</v>
+        <v>0.1020784982968239</v>
       </c>
       <c r="T10">
-        <v>0.7266278764120904</v>
+        <v>0.7334974952997341</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.06184924352192</v>
+        <v>23.16608821646393</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09673938345010973</v>
+        <v>0.09663106203584197</v>
       </c>
       <c r="C11">
-        <v>45.25677827329636</v>
+        <v>44.86011793773107</v>
       </c>
       <c r="D11">
-        <v>47.48477827329635</v>
+        <v>47.56011793773106</v>
       </c>
       <c r="E11">
-        <v>-6.052</v>
+        <v>-5.580000000000001</v>
       </c>
       <c r="F11">
-        <v>4.248</v>
+        <v>4.72</v>
       </c>
       <c r="G11">
         <v>2.02</v>
@@ -2189,28 +2189,28 @@
         <v>4.95</v>
       </c>
       <c r="M11">
-        <v>0.2136744</v>
+        <v>0.237416</v>
       </c>
       <c r="N11">
-        <v>4.7363256</v>
+        <v>4.712584000000001</v>
       </c>
       <c r="O11">
-        <v>0.71044884</v>
+        <v>0.7068876000000001</v>
       </c>
       <c r="P11">
-        <v>4.02587676</v>
+        <v>4.005696400000001</v>
       </c>
       <c r="Q11">
-        <v>5.74587676</v>
+        <v>5.7256964</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1020784982968239</v>
+        <v>0.1026172911509355</v>
       </c>
       <c r="T11">
-        <v>0.7334974952997341</v>
+        <v>0.7405197723848812</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.16608821646393</v>
+        <v>20.84947939481754</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09663106203584197</v>
+        <v>0.09652274062157418</v>
       </c>
       <c r="C12">
-        <v>44.86011793773107</v>
+        <v>44.46369705090022</v>
       </c>
       <c r="D12">
-        <v>47.56011793773106</v>
+        <v>47.63569705090022</v>
       </c>
       <c r="E12">
-        <v>-5.58</v>
+        <v>-5.108000000000001</v>
       </c>
       <c r="F12">
-        <v>4.720000000000001</v>
+        <v>5.192</v>
       </c>
       <c r="G12">
         <v>2.02</v>
@@ -2271,28 +2271,28 @@
         <v>4.95</v>
       </c>
       <c r="M12">
-        <v>0.237416</v>
+        <v>0.2611576</v>
       </c>
       <c r="N12">
-        <v>4.712584000000001</v>
+        <v>4.6888424</v>
       </c>
       <c r="O12">
-        <v>0.7068876000000001</v>
+        <v>0.70332636</v>
       </c>
       <c r="P12">
-        <v>4.005696400000001</v>
+        <v>3.98551604</v>
       </c>
       <c r="Q12">
-        <v>5.7256964</v>
+        <v>5.70551604</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1026172911509355</v>
+        <v>0.1031681917096339</v>
       </c>
       <c r="T12">
-        <v>0.7405197723848812</v>
+        <v>0.7476998534494697</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.84947939481754</v>
+        <v>18.95407217710685</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09652274062157418</v>
+        <v>0.0964144192073064</v>
       </c>
       <c r="C13">
-        <v>44.46369705090022</v>
+        <v>44.06751675616478</v>
       </c>
       <c r="D13">
-        <v>47.63569705090022</v>
+        <v>47.71151675616478</v>
       </c>
       <c r="E13">
-        <v>-5.108000000000001</v>
+        <v>-4.636000000000001</v>
       </c>
       <c r="F13">
-        <v>5.192</v>
+        <v>5.664</v>
       </c>
       <c r="G13">
         <v>2.02</v>
@@ -2353,28 +2353,28 @@
         <v>4.95</v>
       </c>
       <c r="M13">
-        <v>0.2611576</v>
+        <v>0.2848992</v>
       </c>
       <c r="N13">
-        <v>4.6888424</v>
+        <v>4.6651008</v>
       </c>
       <c r="O13">
-        <v>0.70332636</v>
+        <v>0.69976512</v>
       </c>
       <c r="P13">
-        <v>3.98551604</v>
+        <v>3.96533568</v>
       </c>
       <c r="Q13">
-        <v>5.70551604</v>
+        <v>5.68533568</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1031681917096339</v>
+        <v>0.1037316127355754</v>
       </c>
       <c r="T13">
-        <v>0.7476998534494697</v>
+        <v>0.7550431181746169</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.95407217710685</v>
+        <v>17.37456616234795</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0964144192073064</v>
+        <v>0.0963060977930386</v>
       </c>
       <c r="C14">
-        <v>44.06751675616478</v>
+        <v>43.67157820417668</v>
       </c>
       <c r="D14">
-        <v>47.71151675616478</v>
+        <v>47.78757820417668</v>
       </c>
       <c r="E14">
-        <v>-4.636000000000001</v>
+        <v>-4.164</v>
       </c>
       <c r="F14">
-        <v>5.664</v>
+        <v>6.136000000000001</v>
       </c>
       <c r="G14">
         <v>2.02</v>
@@ -2435,28 +2435,28 @@
         <v>4.95</v>
       </c>
       <c r="M14">
-        <v>0.2848992</v>
+        <v>0.3086408</v>
       </c>
       <c r="N14">
-        <v>4.6651008</v>
+        <v>4.6413592</v>
       </c>
       <c r="O14">
-        <v>0.69976512</v>
+        <v>0.69620388</v>
       </c>
       <c r="P14">
-        <v>3.96533568</v>
+        <v>3.94515532</v>
       </c>
       <c r="Q14">
-        <v>5.68533568</v>
+        <v>5.66515532</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1037316127355754</v>
+        <v>0.1043079859690099</v>
       </c>
       <c r="T14">
-        <v>0.7550431181746169</v>
+        <v>0.7625551935831009</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.37456616234795</v>
+        <v>16.03806107293656</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0963060977930386</v>
+        <v>0.09619777637877082</v>
       </c>
       <c r="C15">
-        <v>43.67157820417668</v>
+        <v>43.27588255293703</v>
       </c>
       <c r="D15">
-        <v>47.78757820417668</v>
+        <v>47.86388255293703</v>
       </c>
       <c r="E15">
-        <v>-4.164</v>
+        <v>-3.691999999999999</v>
       </c>
       <c r="F15">
-        <v>6.136000000000001</v>
+        <v>6.608000000000001</v>
       </c>
       <c r="G15">
         <v>2.02</v>
@@ -2517,28 +2517,28 @@
         <v>4.95</v>
       </c>
       <c r="M15">
-        <v>0.3086408</v>
+        <v>0.3323824000000001</v>
       </c>
       <c r="N15">
-        <v>4.6413592</v>
+        <v>4.6176176</v>
       </c>
       <c r="O15">
-        <v>0.69620388</v>
+        <v>0.69264264</v>
       </c>
       <c r="P15">
-        <v>3.94515532</v>
+        <v>3.92497496</v>
       </c>
       <c r="Q15">
-        <v>5.66515532</v>
+        <v>5.64497496</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1043079859690099</v>
+        <v>0.1048977632311289</v>
       </c>
       <c r="T15">
-        <v>0.7625551935831009</v>
+        <v>0.7702419684196892</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.03806107293656</v>
+        <v>14.89248528201252</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09619777637877082</v>
+        <v>0.09608945496450304</v>
       </c>
       <c r="C16">
-        <v>43.27588255293703</v>
+        <v>42.88043096785488</v>
       </c>
       <c r="D16">
-        <v>47.86388255293703</v>
+        <v>47.94043096785488</v>
       </c>
       <c r="E16">
-        <v>-3.691999999999999</v>
+        <v>-3.219999999999999</v>
       </c>
       <c r="F16">
-        <v>6.608000000000001</v>
+        <v>7.080000000000002</v>
       </c>
       <c r="G16">
         <v>2.02</v>
@@ -2599,28 +2599,28 @@
         <v>4.95</v>
       </c>
       <c r="M16">
-        <v>0.3323824000000001</v>
+        <v>0.3561240000000001</v>
       </c>
       <c r="N16">
-        <v>4.6176176</v>
+        <v>4.593876</v>
       </c>
       <c r="O16">
-        <v>0.69264264</v>
+        <v>0.6890814</v>
       </c>
       <c r="P16">
-        <v>3.92497496</v>
+        <v>3.9047946</v>
       </c>
       <c r="Q16">
-        <v>5.64497496</v>
+        <v>5.6247946</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1048977632311289</v>
+        <v>0.1055014176052977</v>
       </c>
       <c r="T16">
-        <v>0.7702419684196892</v>
+        <v>0.7781096085465501</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.89248528201252</v>
+        <v>13.89965292987836</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09608945496450304</v>
+        <v>0.09598113355023527</v>
       </c>
       <c r="C17">
-        <v>42.88043096785488</v>
+        <v>42.48522462180655</v>
       </c>
       <c r="D17">
-        <v>47.94043096785488</v>
+        <v>48.01722462180655</v>
       </c>
       <c r="E17">
-        <v>-3.220000000000001</v>
+        <v>-2.748</v>
       </c>
       <c r="F17">
-        <v>7.08</v>
+        <v>7.552</v>
       </c>
       <c r="G17">
         <v>2.02</v>
@@ -2681,28 +2681,28 @@
         <v>4.95</v>
       </c>
       <c r="M17">
-        <v>0.356124</v>
+        <v>0.3798656</v>
       </c>
       <c r="N17">
-        <v>4.593876</v>
+        <v>4.570134400000001</v>
       </c>
       <c r="O17">
-        <v>0.6890814</v>
+        <v>0.68552016</v>
       </c>
       <c r="P17">
-        <v>3.9047946</v>
+        <v>3.88461424</v>
       </c>
       <c r="Q17">
-        <v>5.6247946</v>
+        <v>5.60461424</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1055014176052977</v>
+        <v>0.106119444702661</v>
       </c>
       <c r="T17">
-        <v>0.7781096085465501</v>
+        <v>0.7861645734383365</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.89965292987836</v>
+        <v>13.03092462176096</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09598113355023527</v>
+        <v>0.09608956213596749</v>
       </c>
       <c r="C18">
-        <v>42.48522462180655</v>
+        <v>41.93635511108106</v>
       </c>
       <c r="D18">
-        <v>48.01722462180655</v>
+        <v>47.94035511108105</v>
       </c>
       <c r="E18">
-        <v>-2.748</v>
+        <v>-2.276</v>
       </c>
       <c r="F18">
-        <v>7.552</v>
+        <v>8.024000000000001</v>
       </c>
       <c r="G18">
         <v>2.02</v>
@@ -2763,45 +2763,45 @@
         <v>4.95</v>
       </c>
       <c r="M18">
-        <v>0.3798656</v>
+        <v>0.4156432</v>
       </c>
       <c r="N18">
-        <v>4.570134400000001</v>
+        <v>4.5343568</v>
       </c>
       <c r="O18">
-        <v>0.68552016</v>
+        <v>0.6801535200000001</v>
       </c>
       <c r="P18">
-        <v>3.88461424</v>
+        <v>3.85420328</v>
       </c>
       <c r="Q18">
-        <v>5.60461424</v>
+        <v>5.57420328</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.106119444702661</v>
+        <v>0.1067523640192379</v>
       </c>
       <c r="T18">
-        <v>0.7861645734383365</v>
+        <v>0.7944136338696838</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.15</v>
       </c>
       <c r="W18">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.03092462176096</v>
+        <v>11.90925293617218</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09608956213596749</v>
+        <v>0.0959939907216997</v>
       </c>
       <c r="C19">
-        <v>41.93635511108106</v>
+        <v>41.53209676114744</v>
       </c>
       <c r="D19">
-        <v>47.94035511108105</v>
+        <v>48.00809676114743</v>
       </c>
       <c r="E19">
-        <v>-2.276</v>
+        <v>-1.803999999999998</v>
       </c>
       <c r="F19">
-        <v>8.024000000000001</v>
+        <v>8.496000000000002</v>
       </c>
       <c r="G19">
         <v>2.02</v>
@@ -2845,28 +2845,28 @@
         <v>4.95</v>
       </c>
       <c r="M19">
-        <v>0.4156432</v>
+        <v>0.4400928000000001</v>
       </c>
       <c r="N19">
-        <v>4.5343568</v>
+        <v>4.5099072</v>
       </c>
       <c r="O19">
-        <v>0.6801535200000001</v>
+        <v>0.67648608</v>
       </c>
       <c r="P19">
-        <v>3.85420328</v>
+        <v>3.83342112</v>
       </c>
       <c r="Q19">
-        <v>5.57420328</v>
+        <v>5.553421119999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1067523640192379</v>
+        <v>0.1074007203923167</v>
       </c>
       <c r="T19">
-        <v>0.7944136338696838</v>
+        <v>0.8028638908969176</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.90925293617218</v>
+        <v>11.2476277730515</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09599399072169972</v>
+        <v>0.09589841930743194</v>
       </c>
       <c r="C20">
-        <v>41.53209676114742</v>
+        <v>41.12803012546637</v>
       </c>
       <c r="D20">
-        <v>48.00809676114742</v>
+        <v>48.07603012546636</v>
       </c>
       <c r="E20">
-        <v>-1.804</v>
+        <v>-1.332000000000001</v>
       </c>
       <c r="F20">
-        <v>8.496</v>
+        <v>8.968</v>
       </c>
       <c r="G20">
         <v>2.02</v>
@@ -2927,28 +2927,28 @@
         <v>4.95</v>
       </c>
       <c r="M20">
-        <v>0.4400928</v>
+        <v>0.4645424</v>
       </c>
       <c r="N20">
-        <v>4.5099072</v>
+        <v>4.4854576</v>
       </c>
       <c r="O20">
-        <v>0.67648608</v>
+        <v>0.67281864</v>
       </c>
       <c r="P20">
-        <v>3.83342112</v>
+        <v>3.81263896</v>
       </c>
       <c r="Q20">
-        <v>5.553421119999999</v>
+        <v>5.53263896</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1074007203923167</v>
+        <v>0.1080650855647308</v>
       </c>
       <c r="T20">
-        <v>0.8028638908969176</v>
+        <v>0.8115227962458116</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.2476277730515</v>
+        <v>10.65564736394353</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09589841930743194</v>
+        <v>0.09580284789316415</v>
       </c>
       <c r="C21">
-        <v>41.12803012546637</v>
+        <v>40.72415601904096</v>
       </c>
       <c r="D21">
-        <v>48.07603012546636</v>
+        <v>48.14415601904096</v>
       </c>
       <c r="E21">
-        <v>-1.332000000000001</v>
+        <v>-0.8599999999999994</v>
       </c>
       <c r="F21">
-        <v>8.968</v>
+        <v>9.440000000000001</v>
       </c>
       <c r="G21">
         <v>2.02</v>
@@ -3009,28 +3009,28 @@
         <v>4.95</v>
       </c>
       <c r="M21">
-        <v>0.4645424</v>
+        <v>0.488992</v>
       </c>
       <c r="N21">
-        <v>4.4854576</v>
+        <v>4.461008000000001</v>
       </c>
       <c r="O21">
-        <v>0.67281864</v>
+        <v>0.6691512000000001</v>
       </c>
       <c r="P21">
-        <v>3.81263896</v>
+        <v>3.791856800000001</v>
       </c>
       <c r="Q21">
-        <v>5.53263896</v>
+        <v>5.5118568</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1080650855647308</v>
+        <v>0.1087460598664552</v>
       </c>
       <c r="T21">
-        <v>0.8115227962458116</v>
+        <v>0.8203981742284279</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.65564736394353</v>
+        <v>10.12286499574635</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09580284789316415</v>
+        <v>0.09601072647889637</v>
       </c>
       <c r="C22">
-        <v>40.72415601904096</v>
+        <v>40.10422052243936</v>
       </c>
       <c r="D22">
-        <v>48.14415601904096</v>
+        <v>47.99622052243936</v>
       </c>
       <c r="E22">
-        <v>-0.8599999999999994</v>
+        <v>-0.3879999999999999</v>
       </c>
       <c r="F22">
-        <v>9.440000000000001</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="G22">
         <v>2.02</v>
@@ -3091,45 +3091,45 @@
         <v>4.95</v>
       </c>
       <c r="M22">
-        <v>0.488992</v>
+        <v>0.530292</v>
       </c>
       <c r="N22">
-        <v>4.461008000000001</v>
+        <v>4.419708</v>
       </c>
       <c r="O22">
-        <v>0.6691512000000001</v>
+        <v>0.6629562</v>
       </c>
       <c r="P22">
-        <v>3.791856800000001</v>
+        <v>3.7567518</v>
       </c>
       <c r="Q22">
-        <v>5.5118568</v>
+        <v>5.4767518</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1087460598664552</v>
+        <v>0.1094442740239195</v>
       </c>
       <c r="T22">
-        <v>0.8203981742284279</v>
+        <v>0.8294982453245282</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.15</v>
       </c>
       <c r="W22">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.12286499574635</v>
+        <v>9.334479871467041</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09601072647889637</v>
+        <v>0.09592960506462861</v>
       </c>
       <c r="C23">
-        <v>40.10422052243936</v>
+        <v>39.68984177440919</v>
       </c>
       <c r="D23">
-        <v>47.99622052243936</v>
+        <v>48.05384177440919</v>
       </c>
       <c r="E23">
-        <v>-0.3879999999999999</v>
+        <v>0.08399999999999963</v>
       </c>
       <c r="F23">
-        <v>9.912000000000001</v>
+        <v>10.384</v>
       </c>
       <c r="G23">
         <v>2.02</v>
@@ -3173,28 +3173,28 @@
         <v>4.95</v>
       </c>
       <c r="M23">
-        <v>0.530292</v>
+        <v>0.555544</v>
       </c>
       <c r="N23">
-        <v>4.419708</v>
+        <v>4.394456</v>
       </c>
       <c r="O23">
-        <v>0.6629562</v>
+        <v>0.6591684</v>
       </c>
       <c r="P23">
-        <v>3.7567518</v>
+        <v>3.7352876</v>
       </c>
       <c r="Q23">
-        <v>5.4767518</v>
+        <v>5.4552876</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1094442740239195</v>
+        <v>0.1101603911084982</v>
       </c>
       <c r="T23">
-        <v>0.8294982453245281</v>
+        <v>0.8388316515769387</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.334479871467041</v>
+        <v>8.910185331854901</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09592960506462861</v>
+        <v>0.09584848365036082</v>
       </c>
       <c r="C24">
-        <v>39.68984177440919</v>
+        <v>39.2756015455986</v>
       </c>
       <c r="D24">
-        <v>48.05384177440919</v>
+        <v>48.1116015455986</v>
       </c>
       <c r="E24">
-        <v>0.08399999999999963</v>
+        <v>0.5560000000000009</v>
       </c>
       <c r="F24">
-        <v>10.384</v>
+        <v>10.856</v>
       </c>
       <c r="G24">
         <v>2.02</v>
@@ -3255,28 +3255,28 @@
         <v>4.95</v>
       </c>
       <c r="M24">
-        <v>0.555544</v>
+        <v>0.5807960000000001</v>
       </c>
       <c r="N24">
-        <v>4.394456</v>
+        <v>4.369204</v>
       </c>
       <c r="O24">
-        <v>0.6591684</v>
+        <v>0.6553806</v>
       </c>
       <c r="P24">
-        <v>3.7352876</v>
+        <v>3.7138234</v>
       </c>
       <c r="Q24">
-        <v>5.4552876</v>
+        <v>5.4338234</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1101603911084982</v>
+        <v>0.1108951086368322</v>
       </c>
       <c r="T24">
-        <v>0.8388316515769387</v>
+        <v>0.8484074839657755</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.910185331854901</v>
+        <v>8.52278596960034</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09584848365036082</v>
+        <v>0.09576736223609303</v>
       </c>
       <c r="C25">
-        <v>39.2756015455986</v>
+        <v>38.86150033610076</v>
       </c>
       <c r="D25">
-        <v>48.1116015455986</v>
+        <v>48.16950033610076</v>
       </c>
       <c r="E25">
-        <v>0.5560000000000009</v>
+        <v>1.028</v>
       </c>
       <c r="F25">
-        <v>10.856</v>
+        <v>11.328</v>
       </c>
       <c r="G25">
         <v>2.02</v>
@@ -3337,28 +3337,28 @@
         <v>4.95</v>
       </c>
       <c r="M25">
-        <v>0.5807960000000001</v>
+        <v>0.606048</v>
       </c>
       <c r="N25">
-        <v>4.369204</v>
+        <v>4.343952</v>
       </c>
       <c r="O25">
-        <v>0.6553806</v>
+        <v>0.6515928</v>
       </c>
       <c r="P25">
-        <v>3.7138234</v>
+        <v>3.6923592</v>
       </c>
       <c r="Q25">
-        <v>5.4338234</v>
+        <v>5.412359199999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1108951086368322</v>
+        <v>0.1116491608369645</v>
       </c>
       <c r="T25">
-        <v>0.8484074839657755</v>
+        <v>0.8582353119437922</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.52278596960034</v>
+        <v>8.167669887533659</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09576736223609303</v>
+        <v>0.09568624082182524</v>
       </c>
       <c r="C26">
-        <v>38.86150033610076</v>
+        <v>38.44753864841913</v>
       </c>
       <c r="D26">
-        <v>48.16950033610076</v>
+        <v>48.22753864841913</v>
       </c>
       <c r="E26">
-        <v>1.027999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="F26">
-        <v>11.328</v>
+        <v>11.8</v>
       </c>
       <c r="G26">
         <v>2.02</v>
@@ -3419,28 +3419,28 @@
         <v>4.95</v>
       </c>
       <c r="M26">
-        <v>0.6060479999999999</v>
+        <v>0.6313</v>
       </c>
       <c r="N26">
-        <v>4.343952</v>
+        <v>4.3187</v>
       </c>
       <c r="O26">
-        <v>0.6515928</v>
+        <v>0.647805</v>
       </c>
       <c r="P26">
-        <v>3.6923592</v>
+        <v>3.670895</v>
       </c>
       <c r="Q26">
-        <v>5.412359199999999</v>
+        <v>5.390895</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1116491608369645</v>
+        <v>0.112423321095767</v>
       </c>
       <c r="T26">
-        <v>0.8582353119437922</v>
+        <v>0.868325215334556</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.167669887533663</v>
+        <v>7.840963092032315</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09568624082182524</v>
+        <v>0.09578191940755748</v>
       </c>
       <c r="C27">
-        <v>38.44753864841913</v>
+        <v>37.90710018796429</v>
       </c>
       <c r="D27">
-        <v>48.22753864841913</v>
+        <v>48.15910018796428</v>
       </c>
       <c r="E27">
-        <v>1.5</v>
+        <v>1.972000000000001</v>
       </c>
       <c r="F27">
-        <v>11.8</v>
+        <v>12.272</v>
       </c>
       <c r="G27">
         <v>2.02</v>
@@ -3501,45 +3501,45 @@
         <v>4.95</v>
       </c>
       <c r="M27">
-        <v>0.6313</v>
+        <v>0.6663696000000001</v>
       </c>
       <c r="N27">
-        <v>4.3187</v>
+        <v>4.2836304</v>
       </c>
       <c r="O27">
-        <v>0.647805</v>
+        <v>0.6425445599999999</v>
       </c>
       <c r="P27">
-        <v>3.670895</v>
+        <v>3.64108584</v>
       </c>
       <c r="Q27">
-        <v>5.390895</v>
+        <v>5.361085839999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.112423321095767</v>
+        <v>0.1132184046048074</v>
       </c>
       <c r="T27">
-        <v>0.868325215334556</v>
+        <v>0.878687818816962</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.840963092032315</v>
+        <v>7.428310054960489</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09578191940755748</v>
+        <v>0.09570759799328971</v>
       </c>
       <c r="C28">
-        <v>37.90710018796429</v>
+        <v>37.48824510182993</v>
       </c>
       <c r="D28">
-        <v>48.15910018796428</v>
+        <v>48.21224510182993</v>
       </c>
       <c r="E28">
-        <v>1.972000000000001</v>
+        <v>2.444000000000001</v>
       </c>
       <c r="F28">
-        <v>12.272</v>
+        <v>12.744</v>
       </c>
       <c r="G28">
         <v>2.02</v>
@@ -3583,28 +3583,28 @@
         <v>4.95</v>
       </c>
       <c r="M28">
-        <v>0.6663696000000001</v>
+        <v>0.6919992000000001</v>
       </c>
       <c r="N28">
-        <v>4.2836304</v>
+        <v>4.2580008</v>
       </c>
       <c r="O28">
-        <v>0.6425445599999999</v>
+        <v>0.6387001199999999</v>
       </c>
       <c r="P28">
-        <v>3.64108584</v>
+        <v>3.61930068</v>
       </c>
       <c r="Q28">
-        <v>5.361085839999999</v>
+        <v>5.339300679999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1132184046048074</v>
+        <v>0.1140352712236845</v>
       </c>
       <c r="T28">
-        <v>0.878687818816962</v>
+        <v>0.8893343292440917</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.428310054960489</v>
+        <v>7.153187460332322</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09570759799328971</v>
+        <v>0.09563327657902193</v>
       </c>
       <c r="C29">
-        <v>37.48824510182993</v>
+        <v>37.06950743907294</v>
       </c>
       <c r="D29">
-        <v>48.21224510182993</v>
+        <v>48.26550743907293</v>
       </c>
       <c r="E29">
-        <v>2.444000000000001</v>
+        <v>2.916000000000002</v>
       </c>
       <c r="F29">
-        <v>12.744</v>
+        <v>13.216</v>
       </c>
       <c r="G29">
         <v>2.02</v>
@@ -3665,28 +3665,28 @@
         <v>4.95</v>
       </c>
       <c r="M29">
-        <v>0.6919992000000001</v>
+        <v>0.7176288000000002</v>
       </c>
       <c r="N29">
-        <v>4.2580008</v>
+        <v>4.2323712</v>
       </c>
       <c r="O29">
-        <v>0.6387001199999999</v>
+        <v>0.63485568</v>
       </c>
       <c r="P29">
-        <v>3.61930068</v>
+        <v>3.59751552</v>
       </c>
       <c r="Q29">
-        <v>5.339300679999999</v>
+        <v>5.31751552</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1140352712236845</v>
+        <v>0.1148748285819749</v>
       </c>
       <c r="T29">
-        <v>0.8893343292440917</v>
+        <v>0.9002765760719749</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.153187460332322</v>
+        <v>6.897716479606168</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09563327657902193</v>
+        <v>0.09555895516475416</v>
       </c>
       <c r="C30">
-        <v>37.06950743907294</v>
+        <v>36.65088758929313</v>
       </c>
       <c r="D30">
-        <v>48.26550743907293</v>
+        <v>48.31888758929313</v>
       </c>
       <c r="E30">
-        <v>2.916000000000002</v>
+        <v>3.388000000000002</v>
       </c>
       <c r="F30">
-        <v>13.216</v>
+        <v>13.688</v>
       </c>
       <c r="G30">
         <v>2.02</v>
@@ -3747,28 +3747,28 @@
         <v>4.95</v>
       </c>
       <c r="M30">
-        <v>0.7176288000000002</v>
+        <v>0.7432584000000001</v>
       </c>
       <c r="N30">
-        <v>4.2323712</v>
+        <v>4.2067416</v>
       </c>
       <c r="O30">
-        <v>0.63485568</v>
+        <v>0.63101124</v>
       </c>
       <c r="P30">
-        <v>3.59751552</v>
+        <v>3.57573036</v>
       </c>
       <c r="Q30">
-        <v>5.31751552</v>
+        <v>5.29573036</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1148748285819749</v>
+        <v>0.1157380354433157</v>
       </c>
       <c r="T30">
-        <v>0.9002765760719749</v>
+        <v>0.9115270552048688</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.897716479606168</v>
+        <v>6.659864187205956</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09555895516475416</v>
+        <v>0.09548463375048635</v>
       </c>
       <c r="C31">
-        <v>36.65088758929313</v>
+        <v>36.23238594381577</v>
       </c>
       <c r="D31">
-        <v>48.31888758929313</v>
+        <v>48.37238594381576</v>
       </c>
       <c r="E31">
-        <v>3.388</v>
+        <v>3.859999999999999</v>
       </c>
       <c r="F31">
-        <v>13.688</v>
+        <v>14.16</v>
       </c>
       <c r="G31">
         <v>2.02</v>
@@ -3829,28 +3829,28 @@
         <v>4.95</v>
       </c>
       <c r="M31">
-        <v>0.7432584000000001</v>
+        <v>0.768888</v>
       </c>
       <c r="N31">
-        <v>4.2067416</v>
+        <v>4.181112000000001</v>
       </c>
       <c r="O31">
-        <v>0.63101124</v>
+        <v>0.6271668</v>
       </c>
       <c r="P31">
-        <v>3.57573036</v>
+        <v>3.553945200000001</v>
       </c>
       <c r="Q31">
-        <v>5.29573036</v>
+        <v>5.2739452</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1157380354433157</v>
+        <v>0.1166259053578377</v>
       </c>
       <c r="T31">
-        <v>0.9115270552048688</v>
+        <v>0.9230989765987024</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.659864187205956</v>
+        <v>6.437868714299093</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09548463375048635</v>
+        <v>0.09541031233621858</v>
       </c>
       <c r="C32">
-        <v>36.23238594381577</v>
+        <v>35.81400289570109</v>
       </c>
       <c r="D32">
-        <v>48.37238594381576</v>
+        <v>48.4260028957011</v>
       </c>
       <c r="E32">
-        <v>3.859999999999999</v>
+        <v>4.332000000000001</v>
       </c>
       <c r="F32">
-        <v>14.16</v>
+        <v>14.632</v>
       </c>
       <c r="G32">
         <v>2.02</v>
@@ -3911,28 +3911,28 @@
         <v>4.95</v>
       </c>
       <c r="M32">
-        <v>0.768888</v>
+        <v>0.7945176</v>
       </c>
       <c r="N32">
-        <v>4.181112000000001</v>
+        <v>4.1554824</v>
       </c>
       <c r="O32">
-        <v>0.6271668</v>
+        <v>0.6233223600000001</v>
       </c>
       <c r="P32">
-        <v>3.553945200000001</v>
+        <v>3.53216004</v>
       </c>
       <c r="Q32">
-        <v>5.2739452</v>
+        <v>5.25216004</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1166259053578377</v>
+        <v>0.1175395106322008</v>
       </c>
       <c r="T32">
-        <v>0.9230989765987024</v>
+        <v>0.9350063160039517</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.437868714299093</v>
+        <v>6.230195529966863</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09541031233621858</v>
+        <v>0.0956079909219508</v>
       </c>
       <c r="C33">
-        <v>35.81400289570109</v>
+        <v>35.19965520975053</v>
       </c>
       <c r="D33">
-        <v>48.4260028957011</v>
+        <v>48.28365520975053</v>
       </c>
       <c r="E33">
-        <v>4.332000000000001</v>
+        <v>4.804</v>
       </c>
       <c r="F33">
-        <v>14.632</v>
+        <v>15.104</v>
       </c>
       <c r="G33">
         <v>2.02</v>
@@ -3993,45 +3993,45 @@
         <v>4.95</v>
       </c>
       <c r="M33">
-        <v>0.7945176</v>
+        <v>0.8352512000000001</v>
       </c>
       <c r="N33">
-        <v>4.1554824</v>
+        <v>4.1147488</v>
       </c>
       <c r="O33">
-        <v>0.6233223600000001</v>
+        <v>0.61721232</v>
       </c>
       <c r="P33">
-        <v>3.53216004</v>
+        <v>3.49753648</v>
       </c>
       <c r="Q33">
-        <v>5.25216004</v>
+        <v>5.21753648</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1175395106322008</v>
+        <v>0.1184799866499276</v>
       </c>
       <c r="T33">
-        <v>0.9350063160039517</v>
+        <v>0.9472638712740611</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.230195529966863</v>
+        <v>5.926360836117325</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0956079909219508</v>
+        <v>0.09554216950768302</v>
       </c>
       <c r="C34">
-        <v>35.19965520975053</v>
+        <v>34.77495996429653</v>
       </c>
       <c r="D34">
-        <v>48.28365520975053</v>
+        <v>48.33095996429653</v>
       </c>
       <c r="E34">
-        <v>4.804</v>
+        <v>5.276000000000002</v>
       </c>
       <c r="F34">
-        <v>15.104</v>
+        <v>15.576</v>
       </c>
       <c r="G34">
         <v>2.02</v>
@@ -4075,28 +4075,28 @@
         <v>4.95</v>
       </c>
       <c r="M34">
-        <v>0.8352512000000001</v>
+        <v>0.8613528000000001</v>
       </c>
       <c r="N34">
-        <v>4.1147488</v>
+        <v>4.0886472</v>
       </c>
       <c r="O34">
-        <v>0.61721232</v>
+        <v>0.61329708</v>
       </c>
       <c r="P34">
-        <v>3.49753648</v>
+        <v>3.47535012</v>
       </c>
       <c r="Q34">
-        <v>5.21753648</v>
+        <v>5.195350120000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1184799866499276</v>
+        <v>0.1194485365786314</v>
       </c>
       <c r="T34">
-        <v>0.9472638712740611</v>
+        <v>0.9598873237164127</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.926360836117325</v>
+        <v>5.746774144113771</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09554216950768302</v>
+        <v>0.09547634809341524</v>
       </c>
       <c r="C35">
-        <v>34.77495996429653</v>
+        <v>34.3503575011439</v>
       </c>
       <c r="D35">
-        <v>48.33095996429653</v>
+        <v>48.3783575011439</v>
       </c>
       <c r="E35">
-        <v>5.276000000000002</v>
+        <v>5.748000000000001</v>
       </c>
       <c r="F35">
-        <v>15.576</v>
+        <v>16.048</v>
       </c>
       <c r="G35">
         <v>2.02</v>
@@ -4157,28 +4157,28 @@
         <v>4.95</v>
       </c>
       <c r="M35">
-        <v>0.8613528000000001</v>
+        <v>0.8874544000000001</v>
       </c>
       <c r="N35">
-        <v>4.0886472</v>
+        <v>4.0625456</v>
       </c>
       <c r="O35">
-        <v>0.61329708</v>
+        <v>0.60938184</v>
       </c>
       <c r="P35">
-        <v>3.47535012</v>
+        <v>3.45316376</v>
       </c>
       <c r="Q35">
-        <v>5.195350120000001</v>
+        <v>5.17316376</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1194485365786314</v>
+        <v>0.1204464365051746</v>
       </c>
       <c r="T35">
-        <v>0.9598873237164127</v>
+        <v>0.9728933050206537</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.746774144113771</v>
+        <v>5.577751375169248</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09547634809341524</v>
+        <v>0.09541052667914746</v>
       </c>
       <c r="C36">
-        <v>34.3503575011439</v>
+        <v>33.92584809353177</v>
       </c>
       <c r="D36">
-        <v>48.3783575011439</v>
+        <v>48.42584809353177</v>
       </c>
       <c r="E36">
-        <v>5.748000000000001</v>
+        <v>6.220000000000002</v>
       </c>
       <c r="F36">
-        <v>16.048</v>
+        <v>16.52</v>
       </c>
       <c r="G36">
         <v>2.02</v>
@@ -4239,28 +4239,28 @@
         <v>4.95</v>
       </c>
       <c r="M36">
-        <v>0.8874544000000001</v>
+        <v>0.9135560000000003</v>
       </c>
       <c r="N36">
-        <v>4.0625456</v>
+        <v>4.036443999999999</v>
       </c>
       <c r="O36">
-        <v>0.60938184</v>
+        <v>0.6054665999999999</v>
       </c>
       <c r="P36">
-        <v>3.45316376</v>
+        <v>3.4309774</v>
       </c>
       <c r="Q36">
-        <v>5.17316376</v>
+        <v>5.150977399999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1204464365051746</v>
+        <v>0.1214750410448422</v>
       </c>
       <c r="T36">
-        <v>0.9728933050206537</v>
+        <v>0.9862994703650253</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.577751375169248</v>
+        <v>5.41838705016441</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09541052667914746</v>
+        <v>0.09534470526487968</v>
       </c>
       <c r="C37">
-        <v>33.92584809353177</v>
+        <v>33.50143201577318</v>
       </c>
       <c r="D37">
-        <v>48.42584809353177</v>
+        <v>48.47343201577318</v>
       </c>
       <c r="E37">
-        <v>6.220000000000002</v>
+        <v>6.692000000000004</v>
       </c>
       <c r="F37">
-        <v>16.52</v>
+        <v>16.992</v>
       </c>
       <c r="G37">
         <v>2.02</v>
@@ -4321,28 +4321,28 @@
         <v>4.95</v>
       </c>
       <c r="M37">
-        <v>0.9135560000000003</v>
+        <v>0.9396576000000003</v>
       </c>
       <c r="N37">
-        <v>4.036443999999999</v>
+        <v>4.0103424</v>
       </c>
       <c r="O37">
-        <v>0.6054665999999999</v>
+        <v>0.60155136</v>
       </c>
       <c r="P37">
-        <v>3.4309774</v>
+        <v>3.40879104</v>
       </c>
       <c r="Q37">
-        <v>5.150977399999999</v>
+        <v>5.128791039999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1214750410448422</v>
+        <v>0.1225357894763745</v>
       </c>
       <c r="T37">
-        <v>0.9862994703650253</v>
+        <v>1.000124578376408</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.41838705016441</v>
+        <v>5.267876298770955</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09534470526487969</v>
+        <v>0.09527888385061191</v>
       </c>
       <c r="C38">
-        <v>33.50143201577318</v>
+        <v>33.07710954326045</v>
       </c>
       <c r="D38">
-        <v>48.47343201577317</v>
+        <v>48.52110954326044</v>
       </c>
       <c r="E38">
-        <v>6.692</v>
+        <v>7.164000000000001</v>
       </c>
       <c r="F38">
-        <v>16.992</v>
+        <v>17.464</v>
       </c>
       <c r="G38">
         <v>2.02</v>
@@ -4403,28 +4403,28 @@
         <v>4.95</v>
       </c>
       <c r="M38">
-        <v>0.9396576000000001</v>
+        <v>0.9657592000000002</v>
       </c>
       <c r="N38">
-        <v>4.0103424</v>
+        <v>3.9842408</v>
       </c>
       <c r="O38">
-        <v>0.60155136</v>
+        <v>0.59763612</v>
       </c>
       <c r="P38">
-        <v>3.40879104</v>
+        <v>3.38660468</v>
       </c>
       <c r="Q38">
-        <v>5.128791039999999</v>
+        <v>5.10660468</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1225357894763745</v>
+        <v>0.1236302124612887</v>
       </c>
       <c r="T38">
-        <v>1.000124578376408</v>
+        <v>1.014388578705613</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.267876298770956</v>
+        <v>5.125501263669038</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09527888385061191</v>
+        <v>0.09521306243634411</v>
       </c>
       <c r="C39">
-        <v>33.07710954326045</v>
+        <v>32.65288095247044</v>
       </c>
       <c r="D39">
-        <v>48.52110954326044</v>
+        <v>48.56888095247044</v>
       </c>
       <c r="E39">
-        <v>7.164000000000001</v>
+        <v>7.635999999999999</v>
       </c>
       <c r="F39">
-        <v>17.464</v>
+        <v>17.936</v>
       </c>
       <c r="G39">
         <v>2.02</v>
@@ -4485,28 +4485,28 @@
         <v>4.95</v>
       </c>
       <c r="M39">
-        <v>0.9657592000000002</v>
+        <v>0.9918608</v>
       </c>
       <c r="N39">
-        <v>3.9842408</v>
+        <v>3.9581392</v>
       </c>
       <c r="O39">
-        <v>0.59763612</v>
+        <v>0.59372088</v>
       </c>
       <c r="P39">
-        <v>3.38660468</v>
+        <v>3.36441832</v>
       </c>
       <c r="Q39">
-        <v>5.10660468</v>
+        <v>5.08441832</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1236302124612887</v>
+        <v>0.1247599394134583</v>
       </c>
       <c r="T39">
-        <v>1.014388578705613</v>
+        <v>1.029112708077695</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.125501263669038</v>
+        <v>4.990619651467222</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09521306243634411</v>
+        <v>0.09514724102207635</v>
       </c>
       <c r="C40">
-        <v>32.65288095247044</v>
+        <v>32.22874652096985</v>
       </c>
       <c r="D40">
-        <v>48.56888095247044</v>
+        <v>48.61674652096985</v>
       </c>
       <c r="E40">
-        <v>7.635999999999999</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="F40">
-        <v>17.936</v>
+        <v>18.408</v>
       </c>
       <c r="G40">
         <v>2.02</v>
@@ -4567,28 +4567,28 @@
         <v>4.95</v>
       </c>
       <c r="M40">
-        <v>0.9918608</v>
+        <v>1.0179624</v>
       </c>
       <c r="N40">
-        <v>3.9581392</v>
+        <v>3.9320376</v>
       </c>
       <c r="O40">
-        <v>0.59372088</v>
+        <v>0.58980564</v>
       </c>
       <c r="P40">
-        <v>3.36441832</v>
+        <v>3.34223196</v>
       </c>
       <c r="Q40">
-        <v>5.08441832</v>
+        <v>5.06223196</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1247599394134583</v>
+        <v>0.1259267065935678</v>
       </c>
       <c r="T40">
-        <v>1.029112708077695</v>
+        <v>1.044319595789846</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.990619651467222</v>
+        <v>4.862655045019345</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09514724102207635</v>
+        <v>0.09508141960780857</v>
       </c>
       <c r="C41">
-        <v>32.22874652096985</v>
+        <v>31.80470652742073</v>
       </c>
       <c r="D41">
-        <v>48.61674652096985</v>
+        <v>48.66470652742073</v>
       </c>
       <c r="E41">
-        <v>8.108000000000001</v>
+        <v>8.580000000000002</v>
       </c>
       <c r="F41">
-        <v>18.408</v>
+        <v>18.88</v>
       </c>
       <c r="G41">
         <v>2.02</v>
@@ -4649,28 +4649,28 @@
         <v>4.95</v>
       </c>
       <c r="M41">
-        <v>1.0179624</v>
+        <v>1.044064</v>
       </c>
       <c r="N41">
-        <v>3.9320376</v>
+        <v>3.905936</v>
       </c>
       <c r="O41">
-        <v>0.58980564</v>
+        <v>0.5858904</v>
       </c>
       <c r="P41">
-        <v>3.34223196</v>
+        <v>3.3200456</v>
       </c>
       <c r="Q41">
-        <v>5.06223196</v>
+        <v>5.0400456</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1259267065935678</v>
+        <v>0.1271323660130143</v>
       </c>
       <c r="T41">
-        <v>1.044319595789846</v>
+        <v>1.060033379759068</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.862655045019345</v>
+        <v>4.741088668893861</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09508141960780857</v>
+        <v>0.09501559819354077</v>
       </c>
       <c r="C42">
-        <v>31.80470652742073</v>
+        <v>31.38076125158577</v>
       </c>
       <c r="D42">
-        <v>48.66470652742073</v>
+        <v>48.71276125158577</v>
       </c>
       <c r="E42">
-        <v>8.580000000000002</v>
+        <v>9.052000000000003</v>
       </c>
       <c r="F42">
-        <v>18.88</v>
+        <v>19.352</v>
       </c>
       <c r="G42">
         <v>2.02</v>
@@ -4731,28 +4731,28 @@
         <v>4.95</v>
       </c>
       <c r="M42">
-        <v>1.044064</v>
+        <v>1.0701656</v>
       </c>
       <c r="N42">
-        <v>3.905936</v>
+        <v>3.8798344</v>
       </c>
       <c r="O42">
-        <v>0.5858904</v>
+        <v>0.5819751599999999</v>
       </c>
       <c r="P42">
-        <v>3.3200456</v>
+        <v>3.29785924</v>
       </c>
       <c r="Q42">
-        <v>5.0400456</v>
+        <v>5.01785924</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1271323660130143</v>
+        <v>0.1283788952432895</v>
       </c>
       <c r="T42">
-        <v>1.060033379759068</v>
+        <v>1.076279834371315</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.741088668893861</v>
+        <v>4.62545235989645</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09501559819354077</v>
+        <v>0.09494977677927301</v>
       </c>
       <c r="C43">
-        <v>31.38076125158577</v>
+        <v>30.95691097433374</v>
       </c>
       <c r="D43">
-        <v>48.71276125158577</v>
+        <v>48.76091097433374</v>
       </c>
       <c r="E43">
-        <v>9.052000000000003</v>
+        <v>9.524000000000001</v>
       </c>
       <c r="F43">
-        <v>19.352</v>
+        <v>19.824</v>
       </c>
       <c r="G43">
         <v>2.02</v>
@@ -4813,28 +4813,28 @@
         <v>4.95</v>
       </c>
       <c r="M43">
-        <v>1.0701656</v>
+        <v>1.0962672</v>
       </c>
       <c r="N43">
-        <v>3.8798344</v>
+        <v>3.8537328</v>
       </c>
       <c r="O43">
-        <v>0.5819751599999999</v>
+        <v>0.5780599199999999</v>
       </c>
       <c r="P43">
-        <v>3.29785924</v>
+        <v>3.27567288</v>
       </c>
       <c r="Q43">
-        <v>5.01785924</v>
+        <v>4.99567288</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1283788952432895</v>
+        <v>0.1296684082401259</v>
       </c>
       <c r="T43">
-        <v>1.076279834371315</v>
+        <v>1.093086511556398</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.62545235989645</v>
+        <v>4.515322541803677</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09494977677927301</v>
+        <v>0.09579770536500522</v>
       </c>
       <c r="C44">
-        <v>30.95691097433374</v>
+        <v>29.87182722688179</v>
       </c>
       <c r="D44">
-        <v>48.76091097433374</v>
+        <v>48.14782722688179</v>
       </c>
       <c r="E44">
-        <v>9.524000000000001</v>
+        <v>9.995999999999999</v>
       </c>
       <c r="F44">
-        <v>19.824</v>
+        <v>20.296</v>
       </c>
       <c r="G44">
         <v>2.02</v>
@@ -4895,45 +4895,45 @@
         <v>4.95</v>
       </c>
       <c r="M44">
-        <v>1.0962672</v>
+        <v>1.1731088</v>
       </c>
       <c r="N44">
-        <v>3.8537328</v>
+        <v>3.7768912</v>
       </c>
       <c r="O44">
-        <v>0.5780599199999999</v>
+        <v>0.56653368</v>
       </c>
       <c r="P44">
-        <v>3.27567288</v>
+        <v>3.21035752</v>
       </c>
       <c r="Q44">
-        <v>4.99567288</v>
+        <v>4.930357519999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1296684082401258</v>
+        <v>0.1310031673070267</v>
       </c>
       <c r="T44">
-        <v>1.093086511556398</v>
+        <v>1.110482896712887</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.15</v>
       </c>
       <c r="W44">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.515322541803677</v>
+        <v>4.219557469861278</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09579770536500522</v>
+        <v>0.09575313395073745</v>
       </c>
       <c r="C45">
-        <v>29.87182722688179</v>
+        <v>29.43166985833781</v>
       </c>
       <c r="D45">
-        <v>48.14782722688179</v>
+        <v>48.1796698583378</v>
       </c>
       <c r="E45">
-        <v>9.995999999999999</v>
+        <v>10.468</v>
       </c>
       <c r="F45">
-        <v>20.296</v>
+        <v>20.768</v>
       </c>
       <c r="G45">
         <v>2.02</v>
@@ -4977,28 +4977,28 @@
         <v>4.95</v>
       </c>
       <c r="M45">
-        <v>1.1731088</v>
+        <v>1.2003904</v>
       </c>
       <c r="N45">
-        <v>3.7768912</v>
+        <v>3.7496096</v>
       </c>
       <c r="O45">
-        <v>0.56653368</v>
+        <v>0.5624414400000001</v>
       </c>
       <c r="P45">
-        <v>3.21035752</v>
+        <v>3.18716816</v>
       </c>
       <c r="Q45">
-        <v>4.930357519999999</v>
+        <v>4.907168159999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1310031673070267</v>
+        <v>0.1323855963406026</v>
       </c>
       <c r="T45">
-        <v>1.110482896712887</v>
+        <v>1.128500581339251</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.219557469861278</v>
+        <v>4.12365843645534</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09575313395073745</v>
+        <v>0.09570856253646967</v>
       </c>
       <c r="C46">
-        <v>29.43166985833781</v>
+        <v>28.99155463600311</v>
       </c>
       <c r="D46">
-        <v>48.1796698583378</v>
+        <v>48.21155463600311</v>
       </c>
       <c r="E46">
-        <v>10.468</v>
+        <v>10.94</v>
       </c>
       <c r="F46">
-        <v>20.768</v>
+        <v>21.24</v>
       </c>
       <c r="G46">
         <v>2.02</v>
@@ -5059,28 +5059,28 @@
         <v>4.95</v>
       </c>
       <c r="M46">
-        <v>1.2003904</v>
+        <v>1.227672</v>
       </c>
       <c r="N46">
-        <v>3.7496096</v>
+        <v>3.722328</v>
       </c>
       <c r="O46">
-        <v>0.5624414400000001</v>
+        <v>0.5583492</v>
       </c>
       <c r="P46">
-        <v>3.18716816</v>
+        <v>3.1639788</v>
       </c>
       <c r="Q46">
-        <v>4.907168159999999</v>
+        <v>4.8839788</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1323855963406026</v>
+        <v>0.1338182955208539</v>
       </c>
       <c r="T46">
-        <v>1.128500581339251</v>
+        <v>1.147173454497483</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.12365843645534</v>
+        <v>4.032021582311888</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09570856253646967</v>
+        <v>0.09703249112220189</v>
       </c>
       <c r="C47">
-        <v>28.99155463600311</v>
+        <v>27.59010781377645</v>
       </c>
       <c r="D47">
-        <v>48.21155463600311</v>
+        <v>47.28210781377645</v>
       </c>
       <c r="E47">
-        <v>10.94</v>
+        <v>11.412</v>
       </c>
       <c r="F47">
-        <v>21.24</v>
+        <v>21.712</v>
       </c>
       <c r="G47">
         <v>2.02</v>
@@ -5141,45 +5141,45 @@
         <v>4.95</v>
       </c>
       <c r="M47">
-        <v>1.227672</v>
+        <v>1.3309456</v>
       </c>
       <c r="N47">
-        <v>3.722328</v>
+        <v>3.6190544</v>
       </c>
       <c r="O47">
-        <v>0.5583492</v>
+        <v>0.54285816</v>
       </c>
       <c r="P47">
-        <v>3.1639788</v>
+        <v>3.07619624</v>
       </c>
       <c r="Q47">
-        <v>4.8839788</v>
+        <v>4.79619624</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1338182955208539</v>
+        <v>0.1353040576337072</v>
       </c>
       <c r="T47">
-        <v>1.147173454497483</v>
+        <v>1.166537915550464</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.15</v>
       </c>
       <c r="W47">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.032021582311888</v>
+        <v>3.719160272215483</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09703249112220189</v>
+        <v>0.0970176697079341</v>
       </c>
       <c r="C48">
-        <v>27.59010781377645</v>
+        <v>27.12831460115037</v>
       </c>
       <c r="D48">
-        <v>47.28210781377645</v>
+        <v>47.29231460115037</v>
       </c>
       <c r="E48">
-        <v>11.412</v>
+        <v>11.884</v>
       </c>
       <c r="F48">
-        <v>21.712</v>
+        <v>22.184</v>
       </c>
       <c r="G48">
         <v>2.02</v>
@@ -5223,28 +5223,28 @@
         <v>4.95</v>
       </c>
       <c r="M48">
-        <v>1.3309456</v>
+        <v>1.3598792</v>
       </c>
       <c r="N48">
-        <v>3.6190544</v>
+        <v>3.5901208</v>
       </c>
       <c r="O48">
-        <v>0.54285816</v>
+        <v>0.53851812</v>
       </c>
       <c r="P48">
-        <v>3.07619624</v>
+        <v>3.05160268</v>
       </c>
       <c r="Q48">
-        <v>4.79619624</v>
+        <v>4.77160268</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1353040576337072</v>
+        <v>0.1368458862413851</v>
       </c>
       <c r="T48">
-        <v>1.166537915550464</v>
+        <v>1.186633110982803</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.719160272215483</v>
+        <v>3.640029202593877</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0970176697079341</v>
+        <v>0.09700284829366633</v>
       </c>
       <c r="C49">
-        <v>27.12831460115037</v>
+        <v>26.6665257961536</v>
       </c>
       <c r="D49">
-        <v>47.29231460115037</v>
+        <v>47.3025257961536</v>
       </c>
       <c r="E49">
-        <v>11.884</v>
+        <v>12.356</v>
       </c>
       <c r="F49">
-        <v>22.184</v>
+        <v>22.656</v>
       </c>
       <c r="G49">
         <v>2.02</v>
@@ -5305,28 +5305,28 @@
         <v>4.95</v>
       </c>
       <c r="M49">
-        <v>1.3598792</v>
+        <v>1.3888128</v>
       </c>
       <c r="N49">
-        <v>3.5901208</v>
+        <v>3.5611872</v>
       </c>
       <c r="O49">
-        <v>0.53851812</v>
+        <v>0.53417808</v>
       </c>
       <c r="P49">
-        <v>3.05160268</v>
+        <v>3.02700912</v>
       </c>
       <c r="Q49">
-        <v>4.77160268</v>
+        <v>4.74700912</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1368458862413851</v>
+        <v>0.1384470159493583</v>
       </c>
       <c r="T49">
-        <v>1.186633110982803</v>
+        <v>1.207501198547155</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.640029202593877</v>
+        <v>3.564195260873171</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09700284829366633</v>
+        <v>0.09815422687939854</v>
       </c>
       <c r="C50">
-        <v>26.6665257961536</v>
+        <v>25.41420215327575</v>
       </c>
       <c r="D50">
-        <v>47.3025257961536</v>
+        <v>46.52220215327574</v>
       </c>
       <c r="E50">
-        <v>12.356</v>
+        <v>12.828</v>
       </c>
       <c r="F50">
-        <v>22.656</v>
+        <v>23.128</v>
       </c>
       <c r="G50">
         <v>2.02</v>
@@ -5387,45 +5387,45 @@
         <v>4.95</v>
       </c>
       <c r="M50">
-        <v>1.3888128</v>
+        <v>1.4825048</v>
       </c>
       <c r="N50">
-        <v>3.5611872</v>
+        <v>3.4674952</v>
       </c>
       <c r="O50">
-        <v>0.53417808</v>
+        <v>0.52012428</v>
       </c>
       <c r="P50">
-        <v>3.02700912</v>
+        <v>2.94737092</v>
       </c>
       <c r="Q50">
-        <v>4.74700912</v>
+        <v>4.66737092</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1384470159493583</v>
+        <v>0.1401109350576442</v>
       </c>
       <c r="T50">
-        <v>1.207501198547155</v>
+        <v>1.229187642486579</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.564195260873172</v>
+        <v>3.338943658057633</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09815422687939854</v>
+        <v>0.09816320546513077</v>
       </c>
       <c r="C51">
-        <v>25.41420215327575</v>
+        <v>24.93621824924068</v>
       </c>
       <c r="D51">
-        <v>46.52220215327574</v>
+        <v>46.51621824924068</v>
       </c>
       <c r="E51">
-        <v>12.828</v>
+        <v>13.3</v>
       </c>
       <c r="F51">
-        <v>23.128</v>
+        <v>23.6</v>
       </c>
       <c r="G51">
         <v>2.02</v>
@@ -5469,28 +5469,28 @@
         <v>4.95</v>
       </c>
       <c r="M51">
-        <v>1.4825048</v>
+        <v>1.51276</v>
       </c>
       <c r="N51">
-        <v>3.4674952</v>
+        <v>3.43724</v>
       </c>
       <c r="O51">
-        <v>0.52012428</v>
+        <v>0.515586</v>
       </c>
       <c r="P51">
-        <v>2.94737092</v>
+        <v>2.921654</v>
       </c>
       <c r="Q51">
-        <v>4.66737092</v>
+        <v>4.641654</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1401109350576442</v>
+        <v>0.1418414109302615</v>
       </c>
       <c r="T51">
-        <v>1.229187642486579</v>
+        <v>1.251741544183581</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.338943658057633</v>
+        <v>3.27216478489648</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09816320546513077</v>
+        <v>0.098172184050863</v>
       </c>
       <c r="C52">
-        <v>24.93621824924068</v>
+        <v>24.4582358843633</v>
       </c>
       <c r="D52">
-        <v>46.51621824924068</v>
+        <v>46.5102358843633</v>
       </c>
       <c r="E52">
-        <v>13.3</v>
+        <v>13.772</v>
       </c>
       <c r="F52">
-        <v>23.6</v>
+        <v>24.072</v>
       </c>
       <c r="G52">
         <v>2.02</v>
@@ -5551,28 +5551,28 @@
         <v>4.95</v>
       </c>
       <c r="M52">
-        <v>1.51276</v>
+        <v>1.5430152</v>
       </c>
       <c r="N52">
-        <v>3.43724</v>
+        <v>3.4069848</v>
       </c>
       <c r="O52">
-        <v>0.515586</v>
+        <v>0.51104772</v>
       </c>
       <c r="P52">
-        <v>2.921654</v>
+        <v>2.89593708</v>
       </c>
       <c r="Q52">
-        <v>4.641654</v>
+        <v>4.61593708</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1418414109302615</v>
+        <v>0.143642518471149</v>
       </c>
       <c r="T52">
-        <v>1.251741544183581</v>
+        <v>1.275216013296786</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.27216478489648</v>
+        <v>3.208004691074981</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.098172184050863</v>
+        <v>0.09818116263659522</v>
       </c>
       <c r="C53">
-        <v>24.4582358843633</v>
+        <v>23.98025505804985</v>
       </c>
       <c r="D53">
-        <v>46.5102358843633</v>
+        <v>46.50425505804985</v>
       </c>
       <c r="E53">
-        <v>13.772</v>
+        <v>14.244</v>
       </c>
       <c r="F53">
-        <v>24.072</v>
+        <v>24.544</v>
       </c>
       <c r="G53">
         <v>2.02</v>
@@ -5633,28 +5633,28 @@
         <v>4.95</v>
       </c>
       <c r="M53">
-        <v>1.5430152</v>
+        <v>1.5732704</v>
       </c>
       <c r="N53">
-        <v>3.4069848</v>
+        <v>3.3767296</v>
       </c>
       <c r="O53">
-        <v>0.51104772</v>
+        <v>0.50650944</v>
       </c>
       <c r="P53">
-        <v>2.89593708</v>
+        <v>2.87022016</v>
       </c>
       <c r="Q53">
-        <v>4.61593708</v>
+        <v>4.590220159999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.143642518471149</v>
+        <v>0.1455186721595734</v>
       </c>
       <c r="T53">
-        <v>1.275216013296786</v>
+        <v>1.299668585289709</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.208004691074981</v>
+        <v>3.146312293169693</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09818116263659522</v>
+        <v>0.09819014122232743</v>
       </c>
       <c r="C54">
-        <v>23.98025505804985</v>
+        <v>23.50227576970685</v>
       </c>
       <c r="D54">
-        <v>46.50425505804985</v>
+        <v>46.49827576970685</v>
       </c>
       <c r="E54">
-        <v>14.244</v>
+        <v>14.716</v>
       </c>
       <c r="F54">
-        <v>24.544</v>
+        <v>25.016</v>
       </c>
       <c r="G54">
         <v>2.02</v>
@@ -5715,28 +5715,28 @@
         <v>4.95</v>
       </c>
       <c r="M54">
-        <v>1.5732704</v>
+        <v>1.6035256</v>
       </c>
       <c r="N54">
-        <v>3.3767296</v>
+        <v>3.3464744</v>
       </c>
       <c r="O54">
-        <v>0.50650944</v>
+        <v>0.50197116</v>
       </c>
       <c r="P54">
-        <v>2.87022016</v>
+        <v>2.84450324</v>
       </c>
       <c r="Q54">
-        <v>4.590220159999999</v>
+        <v>4.56450324</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1455186721595734</v>
+        <v>0.1474746621751648</v>
       </c>
       <c r="T54">
-        <v>1.299668585289709</v>
+        <v>1.325161692261054</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.146312293169693</v>
+        <v>3.086947910279698</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09819014122232743</v>
+        <v>0.09819911980805965</v>
       </c>
       <c r="C55">
-        <v>23.50227576970685</v>
+        <v>23.02429801874114</v>
       </c>
       <c r="D55">
-        <v>46.49827576970685</v>
+        <v>46.49229801874114</v>
       </c>
       <c r="E55">
-        <v>14.716</v>
+        <v>15.188</v>
       </c>
       <c r="F55">
-        <v>25.016</v>
+        <v>25.488</v>
       </c>
       <c r="G55">
         <v>2.02</v>
@@ -5797,28 +5797,28 @@
         <v>4.95</v>
       </c>
       <c r="M55">
-        <v>1.6035256</v>
+        <v>1.6337808</v>
       </c>
       <c r="N55">
-        <v>3.3464744</v>
+        <v>3.3162192</v>
       </c>
       <c r="O55">
-        <v>0.50197116</v>
+        <v>0.49743288</v>
       </c>
       <c r="P55">
-        <v>2.84450324</v>
+        <v>2.81878632</v>
       </c>
       <c r="Q55">
-        <v>4.56450324</v>
+        <v>4.53878632</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1474746621751648</v>
+        <v>0.1495156952349123</v>
       </c>
       <c r="T55">
-        <v>1.325161692261054</v>
+        <v>1.351763195187674</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.086947910279698</v>
+        <v>3.029782208237481</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09819911980805965</v>
+        <v>0.1018545983937919</v>
       </c>
       <c r="C56">
-        <v>23.02429801874114</v>
+        <v>20.23990293677718</v>
       </c>
       <c r="D56">
-        <v>46.49229801874114</v>
+        <v>44.17990293677718</v>
       </c>
       <c r="E56">
-        <v>15.188</v>
+        <v>15.66</v>
       </c>
       <c r="F56">
-        <v>25.488</v>
+        <v>25.96</v>
       </c>
       <c r="G56">
         <v>2.02</v>
@@ -5879,45 +5879,45 @@
         <v>4.95</v>
       </c>
       <c r="M56">
-        <v>1.6337808</v>
+        <v>1.866524000000001</v>
       </c>
       <c r="N56">
-        <v>3.3162192</v>
+        <v>3.083476</v>
       </c>
       <c r="O56">
-        <v>0.49743288</v>
+        <v>0.4625213999999999</v>
       </c>
       <c r="P56">
-        <v>2.81878632</v>
+        <v>2.6209546</v>
       </c>
       <c r="Q56">
-        <v>4.53878632</v>
+        <v>4.3409546</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1495156952349123</v>
+        <v>0.1516474408750931</v>
       </c>
       <c r="T56">
-        <v>1.351763195187674</v>
+        <v>1.379546987133256</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.15</v>
       </c>
       <c r="W56">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.029782208237481</v>
+        <v>2.651988401970721</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1018545983937919</v>
+        <v>0.1019298769795241</v>
       </c>
       <c r="C57">
-        <v>20.23990293677718</v>
+        <v>19.72269773751716</v>
       </c>
       <c r="D57">
-        <v>44.17990293677718</v>
+        <v>44.13469773751716</v>
       </c>
       <c r="E57">
-        <v>15.66</v>
+        <v>16.13200000000001</v>
       </c>
       <c r="F57">
-        <v>25.96</v>
+        <v>26.43200000000001</v>
       </c>
       <c r="G57">
         <v>2.02</v>
@@ -5961,28 +5961,28 @@
         <v>4.95</v>
       </c>
       <c r="M57">
-        <v>1.866524000000001</v>
+        <v>1.900460800000001</v>
       </c>
       <c r="N57">
-        <v>3.083476</v>
+        <v>3.0495392</v>
       </c>
       <c r="O57">
-        <v>0.4625213999999999</v>
+        <v>0.45743088</v>
       </c>
       <c r="P57">
-        <v>2.6209546</v>
+        <v>2.59210832</v>
       </c>
       <c r="Q57">
-        <v>4.3409546</v>
+        <v>4.31210832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1516474408750931</v>
+        <v>0.1538760840443729</v>
       </c>
       <c r="T57">
-        <v>1.379546987133256</v>
+        <v>1.408593678712727</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.651988401970721</v>
+        <v>2.604631466221244</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1019298769795241</v>
+        <v>0.1020051555652563</v>
       </c>
       <c r="C58">
-        <v>19.72269773751716</v>
+        <v>19.20558495227831</v>
       </c>
       <c r="D58">
-        <v>44.13469773751716</v>
+        <v>44.08958495227831</v>
       </c>
       <c r="E58">
-        <v>16.13200000000001</v>
+        <v>16.604</v>
       </c>
       <c r="F58">
-        <v>26.43200000000001</v>
+        <v>26.904</v>
       </c>
       <c r="G58">
         <v>2.02</v>
@@ -6043,28 +6043,28 @@
         <v>4.95</v>
       </c>
       <c r="M58">
-        <v>1.900460800000001</v>
+        <v>1.9343976</v>
       </c>
       <c r="N58">
-        <v>3.0495392</v>
+        <v>3.0156024</v>
       </c>
       <c r="O58">
-        <v>0.45743088</v>
+        <v>0.4523403599999999</v>
       </c>
       <c r="P58">
-        <v>2.59210832</v>
+        <v>2.56326204</v>
       </c>
       <c r="Q58">
-        <v>4.31210832</v>
+        <v>4.283262039999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1538760840443729</v>
+        <v>0.1562083850354798</v>
       </c>
       <c r="T58">
-        <v>1.408593678712727</v>
+        <v>1.438991379202872</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.604631466221244</v>
+        <v>2.55893617734017</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1020051555652563</v>
+        <v>0.1020804341509885</v>
       </c>
       <c r="C59">
-        <v>19.20558495227831</v>
+        <v>18.68856429796389</v>
       </c>
       <c r="D59">
-        <v>44.08958495227831</v>
+        <v>44.04456429796389</v>
       </c>
       <c r="E59">
-        <v>16.604</v>
+        <v>17.076</v>
       </c>
       <c r="F59">
-        <v>26.904</v>
+        <v>27.376</v>
       </c>
       <c r="G59">
         <v>2.02</v>
@@ -6125,28 +6125,28 @@
         <v>4.95</v>
       </c>
       <c r="M59">
-        <v>1.9343976</v>
+        <v>1.9683344</v>
       </c>
       <c r="N59">
-        <v>3.0156024</v>
+        <v>2.981665599999999</v>
       </c>
       <c r="O59">
-        <v>0.4523403599999999</v>
+        <v>0.4472498399999999</v>
       </c>
       <c r="P59">
-        <v>2.56326204</v>
+        <v>2.534415759999999</v>
       </c>
       <c r="Q59">
-        <v>4.283262039999999</v>
+        <v>4.254415759999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1562083850354798</v>
+        <v>0.1586517479785441</v>
       </c>
       <c r="T59">
-        <v>1.438991379202872</v>
+        <v>1.470836589240166</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.55893617734017</v>
+        <v>2.514816588075684</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1020804341509885</v>
+        <v>0.1041115627367207</v>
       </c>
       <c r="C60">
-        <v>18.68856429796388</v>
+        <v>17.03561684647418</v>
       </c>
       <c r="D60">
-        <v>44.04456429796387</v>
+        <v>42.86361684647418</v>
       </c>
       <c r="E60">
-        <v>17.076</v>
+        <v>17.548</v>
       </c>
       <c r="F60">
-        <v>27.376</v>
+        <v>27.848</v>
       </c>
       <c r="G60">
         <v>2.02</v>
@@ -6207,45 +6207,45 @@
         <v>4.95</v>
       </c>
       <c r="M60">
-        <v>1.9683344</v>
+        <v>2.1108784</v>
       </c>
       <c r="N60">
-        <v>2.9816656</v>
+        <v>2.8391216</v>
       </c>
       <c r="O60">
-        <v>0.44724984</v>
+        <v>0.42586824</v>
       </c>
       <c r="P60">
-        <v>2.53441576</v>
+        <v>2.41325336</v>
       </c>
       <c r="Q60">
-        <v>4.25441576</v>
+        <v>4.133253359999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1586517479785441</v>
+        <v>0.1612142993578555</v>
       </c>
       <c r="T60">
-        <v>1.470836589240166</v>
+        <v>1.504235224157328</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.15</v>
       </c>
       <c r="W60">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.514816588075685</v>
+        <v>2.344995334643625</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1041115627367207</v>
+        <v>0.104219991322453</v>
       </c>
       <c r="C61">
-        <v>17.03561684647418</v>
+        <v>16.5023518711609</v>
       </c>
       <c r="D61">
-        <v>42.86361684647418</v>
+        <v>42.80235187116089</v>
       </c>
       <c r="E61">
-        <v>17.548</v>
+        <v>18.02</v>
       </c>
       <c r="F61">
-        <v>27.848</v>
+        <v>28.32</v>
       </c>
       <c r="G61">
         <v>2.02</v>
@@ -6289,28 +6289,28 @@
         <v>4.95</v>
       </c>
       <c r="M61">
-        <v>2.1108784</v>
+        <v>2.146656</v>
       </c>
       <c r="N61">
-        <v>2.8391216</v>
+        <v>2.803344</v>
       </c>
       <c r="O61">
-        <v>0.42586824</v>
+        <v>0.4205016</v>
       </c>
       <c r="P61">
-        <v>2.41325336</v>
+        <v>2.3828424</v>
       </c>
       <c r="Q61">
-        <v>4.133253359999999</v>
+        <v>4.1028424</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1612142993578555</v>
+        <v>0.1639049783061324</v>
       </c>
       <c r="T61">
-        <v>1.504235224157328</v>
+        <v>1.539303790820349</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.344995334643625</v>
+        <v>2.305912079066231</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.104219991322453</v>
+        <v>0.1043284199081852</v>
       </c>
       <c r="C62">
-        <v>16.5023518711609</v>
+        <v>15.96926177796917</v>
       </c>
       <c r="D62">
-        <v>42.80235187116089</v>
+        <v>42.74126177796916</v>
       </c>
       <c r="E62">
-        <v>18.02</v>
+        <v>18.492</v>
       </c>
       <c r="F62">
-        <v>28.32</v>
+        <v>28.792</v>
       </c>
       <c r="G62">
         <v>2.02</v>
@@ -6371,28 +6371,28 @@
         <v>4.95</v>
       </c>
       <c r="M62">
-        <v>2.146656</v>
+        <v>2.1824336</v>
       </c>
       <c r="N62">
-        <v>2.803344</v>
+        <v>2.7675664</v>
       </c>
       <c r="O62">
-        <v>0.4205016</v>
+        <v>0.4151349599999999</v>
       </c>
       <c r="P62">
-        <v>2.3828424</v>
+        <v>2.35243144</v>
       </c>
       <c r="Q62">
-        <v>4.1028424</v>
+        <v>4.072431439999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1639049783061324</v>
+        <v>0.1667336407902184</v>
       </c>
       <c r="T62">
-        <v>1.539303790820349</v>
+        <v>1.576170745517371</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.305912079066231</v>
+        <v>2.268110241704489</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1043284199081852</v>
+        <v>0.1044368484939174</v>
       </c>
       <c r="C63">
-        <v>15.96926177796917</v>
+        <v>15.43634581915932</v>
       </c>
       <c r="D63">
-        <v>42.74126177796916</v>
+        <v>42.68034581915932</v>
       </c>
       <c r="E63">
-        <v>18.492</v>
+        <v>18.964</v>
       </c>
       <c r="F63">
-        <v>28.792</v>
+        <v>29.264</v>
       </c>
       <c r="G63">
         <v>2.02</v>
@@ -6453,28 +6453,28 @@
         <v>4.95</v>
       </c>
       <c r="M63">
-        <v>2.1824336</v>
+        <v>2.2182112</v>
       </c>
       <c r="N63">
-        <v>2.7675664</v>
+        <v>2.7317888</v>
       </c>
       <c r="O63">
-        <v>0.4151349599999999</v>
+        <v>0.40976832</v>
       </c>
       <c r="P63">
-        <v>2.35243144</v>
+        <v>2.32202048</v>
       </c>
       <c r="Q63">
-        <v>4.072431439999999</v>
+        <v>4.04202048</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1667336407902184</v>
+        <v>0.1697111802471511</v>
       </c>
       <c r="T63">
-        <v>1.576170745517371</v>
+        <v>1.614978066251078</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.268110241704489</v>
+        <v>2.231527818451192</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1044368484939174</v>
+        <v>0.1045452770796496</v>
       </c>
       <c r="C64">
-        <v>15.43634581915932</v>
+        <v>14.90360325124845</v>
       </c>
       <c r="D64">
-        <v>42.68034581915932</v>
+        <v>42.61960325124845</v>
       </c>
       <c r="E64">
-        <v>18.964</v>
+        <v>19.436</v>
       </c>
       <c r="F64">
-        <v>29.264</v>
+        <v>29.736</v>
       </c>
       <c r="G64">
         <v>2.02</v>
@@ -6535,28 +6535,28 @@
         <v>4.95</v>
       </c>
       <c r="M64">
-        <v>2.2182112</v>
+        <v>2.2539888</v>
       </c>
       <c r="N64">
-        <v>2.7317888</v>
+        <v>2.6960112</v>
       </c>
       <c r="O64">
-        <v>0.40976832</v>
+        <v>0.40440168</v>
       </c>
       <c r="P64">
-        <v>2.32202048</v>
+        <v>2.29160952</v>
       </c>
       <c r="Q64">
-        <v>4.04202048</v>
+        <v>4.01160952</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1697111802471511</v>
+        <v>0.1728496677828368</v>
       </c>
       <c r="T64">
-        <v>1.614978066251078</v>
+        <v>1.655883079997418</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.231527818451192</v>
+        <v>2.19610674196784</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1045452770796496</v>
+        <v>0.1046537056653818</v>
       </c>
       <c r="C65">
-        <v>14.90360325124845</v>
+        <v>14.37103333498009</v>
       </c>
       <c r="D65">
-        <v>42.61960325124845</v>
+        <v>42.55903333498009</v>
       </c>
       <c r="E65">
-        <v>19.436</v>
+        <v>19.908</v>
       </c>
       <c r="F65">
-        <v>29.736</v>
+        <v>30.208</v>
       </c>
       <c r="G65">
         <v>2.02</v>
@@ -6617,28 +6617,28 @@
         <v>4.95</v>
       </c>
       <c r="M65">
-        <v>2.2539888</v>
+        <v>2.2897664</v>
       </c>
       <c r="N65">
-        <v>2.6960112</v>
+        <v>2.6602336</v>
       </c>
       <c r="O65">
-        <v>0.40440168</v>
+        <v>0.39903504</v>
       </c>
       <c r="P65">
-        <v>2.29160952</v>
+        <v>2.26119856</v>
       </c>
       <c r="Q65">
-        <v>4.01160952</v>
+        <v>3.98119856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1728496677828368</v>
+        <v>0.1761625157371718</v>
       </c>
       <c r="T65">
-        <v>1.655883079997418</v>
+        <v>1.699060594507443</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.19610674196784</v>
+        <v>2.161792574124592</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1046537056653818</v>
+        <v>0.1047621342511141</v>
       </c>
       <c r="C66">
-        <v>14.37103333498009</v>
+        <v>13.83863533529427</v>
       </c>
       <c r="D66">
-        <v>42.55903333498009</v>
+        <v>42.49863533529427</v>
       </c>
       <c r="E66">
-        <v>19.908</v>
+        <v>20.38</v>
       </c>
       <c r="F66">
-        <v>30.208</v>
+        <v>30.68</v>
       </c>
       <c r="G66">
         <v>2.02</v>
@@ -6699,28 +6699,28 @@
         <v>4.95</v>
       </c>
       <c r="M66">
-        <v>2.2897664</v>
+        <v>2.325544</v>
       </c>
       <c r="N66">
-        <v>2.6602336</v>
+        <v>2.624456</v>
       </c>
       <c r="O66">
-        <v>0.39903504</v>
+        <v>0.3936684</v>
       </c>
       <c r="P66">
-        <v>2.26119856</v>
+        <v>2.2307876</v>
       </c>
       <c r="Q66">
-        <v>3.98119856</v>
+        <v>3.9507876</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1761625157371718</v>
+        <v>0.1796646692888974</v>
       </c>
       <c r="T66">
-        <v>1.699060594507443</v>
+        <v>1.744705395560898</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.161792574124592</v>
+        <v>2.128534226830367</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1047621342511141</v>
+        <v>0.1048705628368463</v>
       </c>
       <c r="C67">
-        <v>13.83863533529427</v>
+        <v>13.30640852129779</v>
       </c>
       <c r="D67">
-        <v>42.49863533529427</v>
+        <v>42.4384085212978</v>
       </c>
       <c r="E67">
-        <v>20.38</v>
+        <v>20.852</v>
       </c>
       <c r="F67">
-        <v>30.68</v>
+        <v>31.152</v>
       </c>
       <c r="G67">
         <v>2.02</v>
@@ -6781,28 +6781,28 @@
         <v>4.95</v>
       </c>
       <c r="M67">
-        <v>2.325544</v>
+        <v>2.361321600000001</v>
       </c>
       <c r="N67">
-        <v>2.624456</v>
+        <v>2.5886784</v>
       </c>
       <c r="O67">
-        <v>0.3936684</v>
+        <v>0.3883017599999999</v>
       </c>
       <c r="P67">
-        <v>2.2307876</v>
+        <v>2.20037664</v>
       </c>
       <c r="Q67">
-        <v>3.9507876</v>
+        <v>3.920376639999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1796646692888974</v>
+        <v>0.1833728318730774</v>
       </c>
       <c r="T67">
-        <v>1.744705395560898</v>
+        <v>1.793035184911616</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.128534226830367</v>
+        <v>2.096283708242028</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1048705628368463</v>
+        <v>0.1049789914225785</v>
       </c>
       <c r="C68">
-        <v>13.30640852129779</v>
+        <v>12.77435216623471</v>
       </c>
       <c r="D68">
-        <v>42.4384085212978</v>
+        <v>42.37835216623471</v>
       </c>
       <c r="E68">
-        <v>20.852</v>
+        <v>21.324</v>
       </c>
       <c r="F68">
-        <v>31.152</v>
+        <v>31.624</v>
       </c>
       <c r="G68">
         <v>2.02</v>
@@ -6863,28 +6863,28 @@
         <v>4.95</v>
       </c>
       <c r="M68">
-        <v>2.361321600000001</v>
+        <v>2.3970992</v>
       </c>
       <c r="N68">
-        <v>2.5886784</v>
+        <v>2.5529008</v>
       </c>
       <c r="O68">
-        <v>0.3883017599999999</v>
+        <v>0.38293512</v>
       </c>
       <c r="P68">
-        <v>2.20037664</v>
+        <v>2.16996568</v>
       </c>
       <c r="Q68">
-        <v>3.920376639999999</v>
+        <v>3.88996568</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1833728318730774</v>
+        <v>0.1873057315835713</v>
       </c>
       <c r="T68">
-        <v>1.793035184911616</v>
+        <v>1.844294052404801</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.096283708242028</v>
+        <v>2.064995891701102</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1049789914225785</v>
+        <v>0.1050874200083107</v>
       </c>
       <c r="C69">
-        <v>12.77435216623471</v>
+        <v>12.24246554745712</v>
       </c>
       <c r="D69">
-        <v>42.37835216623471</v>
+        <v>42.31846554745712</v>
       </c>
       <c r="E69">
-        <v>21.324</v>
+        <v>21.796</v>
       </c>
       <c r="F69">
-        <v>31.624</v>
+        <v>32.096</v>
       </c>
       <c r="G69">
         <v>2.02</v>
@@ -6945,28 +6945,28 @@
         <v>4.95</v>
       </c>
       <c r="M69">
-        <v>2.3970992</v>
+        <v>2.4328768</v>
       </c>
       <c r="N69">
-        <v>2.5529008</v>
+        <v>2.5171232</v>
       </c>
       <c r="O69">
-        <v>0.38293512</v>
+        <v>0.37756848</v>
       </c>
       <c r="P69">
-        <v>2.16996568</v>
+        <v>2.13955472</v>
       </c>
       <c r="Q69">
-        <v>3.88996568</v>
+        <v>3.85955472</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1873057315835713</v>
+        <v>0.1914844375259711</v>
       </c>
       <c r="T69">
-        <v>1.844294052404801</v>
+        <v>1.89875659911631</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.064995891701102</v>
+        <v>2.03462830505844</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1050874200083107</v>
+        <v>0.105195848594043</v>
       </c>
       <c r="C70">
-        <v>12.24246554745712</v>
+        <v>11.71074794639614</v>
       </c>
       <c r="D70">
-        <v>42.31846554745712</v>
+        <v>42.25874794639614</v>
       </c>
       <c r="E70">
-        <v>21.796</v>
+        <v>22.268</v>
       </c>
       <c r="F70">
-        <v>32.096</v>
+        <v>32.568</v>
       </c>
       <c r="G70">
         <v>2.02</v>
@@ -7027,28 +7027,28 @@
         <v>4.95</v>
       </c>
       <c r="M70">
-        <v>2.4328768</v>
+        <v>2.468654400000001</v>
       </c>
       <c r="N70">
-        <v>2.5171232</v>
+        <v>2.4813456</v>
       </c>
       <c r="O70">
-        <v>0.37756848</v>
+        <v>0.37220184</v>
       </c>
       <c r="P70">
-        <v>2.13955472</v>
+        <v>2.10914376</v>
       </c>
       <c r="Q70">
-        <v>3.85955472</v>
+        <v>3.82914376</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1914844375259711</v>
+        <v>0.1959327374001386</v>
       </c>
       <c r="T70">
-        <v>1.89875659911631</v>
+        <v>1.956732858518885</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.03462830505844</v>
+        <v>2.005140938318462</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.105195848594043</v>
+        <v>0.1137532771797752</v>
       </c>
       <c r="C71">
-        <v>11.71074794639614</v>
+        <v>7.003980989201914</v>
       </c>
       <c r="D71">
-        <v>42.25874794639614</v>
+        <v>38.02398098920192</v>
       </c>
       <c r="E71">
-        <v>22.268</v>
+        <v>22.74000000000001</v>
       </c>
       <c r="F71">
-        <v>32.568</v>
+        <v>33.04000000000001</v>
       </c>
       <c r="G71">
         <v>2.02</v>
@@ -7109,45 +7109,45 @@
         <v>4.95</v>
       </c>
       <c r="M71">
-        <v>2.468654400000001</v>
+        <v>2.9736</v>
       </c>
       <c r="N71">
-        <v>2.4813456</v>
+        <v>1.9764</v>
       </c>
       <c r="O71">
-        <v>0.37220184</v>
+        <v>0.29646</v>
       </c>
       <c r="P71">
-        <v>2.10914376</v>
+        <v>1.67994</v>
       </c>
       <c r="Q71">
-        <v>3.82914376</v>
+        <v>3.39994</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1959327374001386</v>
+        <v>0.2006775905992506</v>
       </c>
       <c r="T71">
-        <v>1.956732858518885</v>
+        <v>2.018574201881631</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.15</v>
       </c>
       <c r="W71">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.005140938318462</v>
+        <v>1.664648910411622</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1137532771797752</v>
+        <v>0.1139824057655074</v>
       </c>
       <c r="C72">
-        <v>7.003980989201914</v>
+        <v>6.430229039856556</v>
       </c>
       <c r="D72">
-        <v>38.02398098920192</v>
+        <v>37.92222903985656</v>
       </c>
       <c r="E72">
-        <v>22.74000000000001</v>
+        <v>23.21200000000001</v>
       </c>
       <c r="F72">
-        <v>33.04000000000001</v>
+        <v>33.51200000000001</v>
       </c>
       <c r="G72">
         <v>2.02</v>
@@ -7191,28 +7191,28 @@
         <v>4.95</v>
       </c>
       <c r="M72">
-        <v>2.9736</v>
+        <v>3.016080000000001</v>
       </c>
       <c r="N72">
-        <v>1.9764</v>
+        <v>1.93392</v>
       </c>
       <c r="O72">
-        <v>0.29646</v>
+        <v>0.290088</v>
       </c>
       <c r="P72">
-        <v>1.67994</v>
+        <v>1.643832</v>
       </c>
       <c r="Q72">
-        <v>3.39994</v>
+        <v>3.363831999999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2006775905992506</v>
+        <v>0.2057496750534739</v>
       </c>
       <c r="T72">
-        <v>2.018574201881631</v>
+        <v>2.08468046547629</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.664648910411622</v>
+        <v>1.64120315111005</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1139824057655074</v>
+        <v>0.1142115343512396</v>
       </c>
       <c r="C73">
-        <v>6.43022903985657</v>
+        <v>5.857020212355565</v>
       </c>
       <c r="D73">
-        <v>37.92222903985657</v>
+        <v>37.82102021235556</v>
       </c>
       <c r="E73">
-        <v>23.212</v>
+        <v>23.684</v>
       </c>
       <c r="F73">
-        <v>33.512</v>
+        <v>33.984</v>
       </c>
       <c r="G73">
         <v>2.02</v>
@@ -7273,28 +7273,28 @@
         <v>4.95</v>
       </c>
       <c r="M73">
-        <v>3.01608</v>
+        <v>3.05856</v>
       </c>
       <c r="N73">
-        <v>1.93392</v>
+        <v>1.89144</v>
       </c>
       <c r="O73">
-        <v>0.290088</v>
+        <v>0.283716</v>
       </c>
       <c r="P73">
-        <v>1.643832</v>
+        <v>1.607724</v>
       </c>
       <c r="Q73">
-        <v>3.363832</v>
+        <v>3.327724</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2057496750534738</v>
+        <v>0.2111840512544272</v>
       </c>
       <c r="T73">
-        <v>2.08468046547629</v>
+        <v>2.155508605041996</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.64120315111005</v>
+        <v>1.618408662900188</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1142115343512396</v>
+        <v>0.1144406629369718</v>
       </c>
       <c r="C74">
-        <v>5.857020212355565</v>
+        <v>5.284350169737728</v>
       </c>
       <c r="D74">
-        <v>37.82102021235556</v>
+        <v>37.72035016973773</v>
       </c>
       <c r="E74">
-        <v>23.684</v>
+        <v>24.156</v>
       </c>
       <c r="F74">
-        <v>33.984</v>
+        <v>34.456</v>
       </c>
       <c r="G74">
         <v>2.02</v>
@@ -7355,28 +7355,28 @@
         <v>4.95</v>
       </c>
       <c r="M74">
-        <v>3.05856</v>
+        <v>3.10104</v>
       </c>
       <c r="N74">
-        <v>1.89144</v>
+        <v>1.84896</v>
       </c>
       <c r="O74">
-        <v>0.283716</v>
+        <v>0.277344</v>
       </c>
       <c r="P74">
-        <v>1.607724</v>
+        <v>1.571616</v>
       </c>
       <c r="Q74">
-        <v>3.327724</v>
+        <v>3.291615999999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2111840512544272</v>
+        <v>0.2170209738406364</v>
       </c>
       <c r="T74">
-        <v>2.155508605041996</v>
+        <v>2.231583273464421</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.618408662900188</v>
+        <v>1.596238681216624</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1144406629369718</v>
+        <v>0.1146697915227041</v>
       </c>
       <c r="C75">
-        <v>5.284350169737728</v>
+        <v>4.712214621094823</v>
       </c>
       <c r="D75">
-        <v>37.72035016973773</v>
+        <v>37.62021462109482</v>
       </c>
       <c r="E75">
-        <v>24.156</v>
+        <v>24.628</v>
       </c>
       <c r="F75">
-        <v>34.456</v>
+        <v>34.928</v>
       </c>
       <c r="G75">
         <v>2.02</v>
@@ -7437,28 +7437,28 @@
         <v>4.95</v>
       </c>
       <c r="M75">
-        <v>3.10104</v>
+        <v>3.14352</v>
       </c>
       <c r="N75">
-        <v>1.84896</v>
+        <v>1.80648</v>
       </c>
       <c r="O75">
-        <v>0.277344</v>
+        <v>0.270972</v>
       </c>
       <c r="P75">
-        <v>1.571616</v>
+        <v>1.535508</v>
       </c>
       <c r="Q75">
-        <v>3.291615999999999</v>
+        <v>3.255508</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2170209738406364</v>
+        <v>0.2233068904719387</v>
       </c>
       <c r="T75">
-        <v>2.231583273464421</v>
+        <v>2.313509839457803</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.596238681216624</v>
+        <v>1.57466788822721</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1146697915227041</v>
+        <v>0.1148989201084363</v>
       </c>
       <c r="C76">
-        <v>4.712214621094823</v>
+        <v>4.140609320962056</v>
       </c>
       <c r="D76">
-        <v>37.62021462109482</v>
+        <v>37.52060932096206</v>
       </c>
       <c r="E76">
-        <v>24.628</v>
+        <v>25.1</v>
       </c>
       <c r="F76">
-        <v>34.928</v>
+        <v>35.40000000000001</v>
       </c>
       <c r="G76">
         <v>2.02</v>
@@ -7519,28 +7519,28 @@
         <v>4.95</v>
       </c>
       <c r="M76">
-        <v>3.14352</v>
+        <v>3.186</v>
       </c>
       <c r="N76">
-        <v>1.80648</v>
+        <v>1.764</v>
       </c>
       <c r="O76">
-        <v>0.270972</v>
+        <v>0.2645999999999999</v>
       </c>
       <c r="P76">
-        <v>1.535508</v>
+        <v>1.4994</v>
       </c>
       <c r="Q76">
-        <v>3.255508</v>
+        <v>3.219399999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2233068904719387</v>
+        <v>0.2300956804337451</v>
       </c>
       <c r="T76">
-        <v>2.313509839457803</v>
+        <v>2.401990530730655</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.57466788822721</v>
+        <v>1.553672316384181</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1148989201084363</v>
+        <v>0.1151280486941685</v>
       </c>
       <c r="C77">
-        <v>4.140609320962056</v>
+        <v>3.56953006871791</v>
       </c>
       <c r="D77">
-        <v>37.52060932096206</v>
+        <v>37.42153006871791</v>
       </c>
       <c r="E77">
-        <v>25.1</v>
+        <v>25.572</v>
       </c>
       <c r="F77">
-        <v>35.40000000000001</v>
+        <v>35.872</v>
       </c>
       <c r="G77">
         <v>2.02</v>
@@ -7601,28 +7601,28 @@
         <v>4.95</v>
       </c>
       <c r="M77">
-        <v>3.186</v>
+        <v>3.22848</v>
       </c>
       <c r="N77">
-        <v>1.764</v>
+        <v>1.72152</v>
       </c>
       <c r="O77">
-        <v>0.2645999999999999</v>
+        <v>0.2582280000000001</v>
       </c>
       <c r="P77">
-        <v>1.4994</v>
+        <v>1.463292</v>
       </c>
       <c r="Q77">
-        <v>3.219399999999999</v>
+        <v>3.183292</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2300956804337451</v>
+        <v>0.2374502028923688</v>
       </c>
       <c r="T77">
-        <v>2.401990530730655</v>
+        <v>2.497844612942911</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.553672316384181</v>
+        <v>1.533229259589652</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1151280486941685</v>
+        <v>0.1153571772799007</v>
       </c>
       <c r="C78">
-        <v>3.56953006871791</v>
+        <v>2.998972707993744</v>
       </c>
       <c r="D78">
-        <v>37.42153006871791</v>
+        <v>37.32297270799374</v>
       </c>
       <c r="E78">
-        <v>25.572</v>
+        <v>26.044</v>
       </c>
       <c r="F78">
-        <v>35.872</v>
+        <v>36.344</v>
       </c>
       <c r="G78">
         <v>2.02</v>
@@ -7683,28 +7683,28 @@
         <v>4.95</v>
       </c>
       <c r="M78">
-        <v>3.22848</v>
+        <v>3.27096</v>
       </c>
       <c r="N78">
-        <v>1.72152</v>
+        <v>1.67904</v>
       </c>
       <c r="O78">
-        <v>0.2582280000000001</v>
+        <v>0.251856</v>
       </c>
       <c r="P78">
-        <v>1.463292</v>
+        <v>1.427184</v>
       </c>
       <c r="Q78">
-        <v>3.183292</v>
+        <v>3.147184</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2374502028923688</v>
+        <v>0.2454442490430466</v>
       </c>
       <c r="T78">
-        <v>2.497844612942911</v>
+        <v>2.602033832738841</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.533229259589652</v>
+        <v>1.513317191283293</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1153571772799007</v>
+        <v>0.1552002652356725</v>
       </c>
       <c r="C79">
-        <v>2.998972707993744</v>
+        <v>-9.196804504256669</v>
       </c>
       <c r="D79">
-        <v>37.32297270799374</v>
+        <v>25.59919549574333</v>
       </c>
       <c r="E79">
-        <v>26.044</v>
+        <v>26.516</v>
       </c>
       <c r="F79">
-        <v>36.344</v>
+        <v>36.816</v>
       </c>
       <c r="G79">
         <v>2.02</v>
@@ -7765,45 +7765,45 @@
         <v>4.95</v>
       </c>
       <c r="M79">
-        <v>3.27096</v>
+        <v>5.404588800000001</v>
       </c>
       <c r="N79">
-        <v>1.67904</v>
+        <v>-0.4545888000000007</v>
       </c>
       <c r="O79">
-        <v>0.251856</v>
+        <v>-0.06818832000000009</v>
       </c>
       <c r="P79">
-        <v>1.427184</v>
+        <v>-0.3864004800000006</v>
       </c>
       <c r="Q79">
-        <v>3.147184</v>
+        <v>1.333599519999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2454442490430466</v>
+        <v>0.2564872610866469</v>
       </c>
       <c r="T79">
-        <v>2.602033832738841</v>
+        <v>2.745961299172373</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.15</v>
+        <v>0.1373832547630635</v>
       </c>
       <c r="W79">
-        <v>0.0765</v>
+        <v>0.1266321382007823</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.513317191283293</v>
+        <v>0.9158883650870904</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1552002652356725</v>
+        <v>0.1562102652356725</v>
       </c>
       <c r="C80">
-        <v>-9.196804504256669</v>
+        <v>-9.871032638077459</v>
       </c>
       <c r="D80">
-        <v>25.59919549574333</v>
+        <v>25.39696736192255</v>
       </c>
       <c r="E80">
-        <v>26.516</v>
+        <v>26.988</v>
       </c>
       <c r="F80">
-        <v>36.816</v>
+        <v>37.288</v>
       </c>
       <c r="G80">
         <v>2.02</v>
@@ -7847,37 +7847,37 @@
         <v>4.95</v>
       </c>
       <c r="M80">
-        <v>5.404588800000001</v>
+        <v>5.473878400000001</v>
       </c>
       <c r="N80">
-        <v>-0.4545888000000007</v>
+        <v>-0.523878400000001</v>
       </c>
       <c r="O80">
-        <v>-0.06818832000000009</v>
+        <v>-0.07858176000000014</v>
       </c>
       <c r="P80">
-        <v>-0.3864004800000006</v>
+        <v>-0.4452966400000008</v>
       </c>
       <c r="Q80">
-        <v>1.333599519999999</v>
+        <v>1.274703359999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2564872610866469</v>
+        <v>0.2665199878050587</v>
       </c>
       <c r="T80">
-        <v>2.745961299172373</v>
+        <v>2.876721361037724</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1373832547630635</v>
+        <v>0.1356442262217589</v>
       </c>
       <c r="W80">
-        <v>0.1266321382007823</v>
+        <v>0.1268874275906458</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9158883650870904</v>
+        <v>0.9042948414783929</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1562102652356725</v>
+        <v>0.1572202652356725</v>
       </c>
       <c r="C81">
-        <v>-9.871032638077459</v>
+        <v>-10.5420906973554</v>
       </c>
       <c r="D81">
-        <v>25.39696736192255</v>
+        <v>25.1979093026446</v>
       </c>
       <c r="E81">
-        <v>26.988</v>
+        <v>27.46</v>
       </c>
       <c r="F81">
-        <v>37.288</v>
+        <v>37.76000000000001</v>
       </c>
       <c r="G81">
         <v>2.02</v>
@@ -7929,37 +7929,37 @@
         <v>4.95</v>
       </c>
       <c r="M81">
-        <v>5.473878400000001</v>
+        <v>5.543168000000001</v>
       </c>
       <c r="N81">
-        <v>-0.523878400000001</v>
+        <v>-0.5931680000000012</v>
       </c>
       <c r="O81">
-        <v>-0.07858176000000014</v>
+        <v>-0.08897520000000018</v>
       </c>
       <c r="P81">
-        <v>-0.4452966400000008</v>
+        <v>-0.5041928000000011</v>
       </c>
       <c r="Q81">
-        <v>1.274703359999999</v>
+        <v>1.215807199999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2665199878050587</v>
+        <v>0.2775559871953117</v>
       </c>
       <c r="T81">
-        <v>2.876721361037724</v>
+        <v>3.020557429089611</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1356442262217589</v>
+        <v>0.1339486733939869</v>
       </c>
       <c r="W81">
-        <v>0.1268874275906458</v>
+        <v>0.1271363347457627</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9042948414783929</v>
+        <v>0.892991155959913</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1572202652356725</v>
+        <v>0.1582302652356725</v>
       </c>
       <c r="C82">
-        <v>-10.5420906973554</v>
+        <v>-11.21005264227094</v>
       </c>
       <c r="D82">
-        <v>25.1979093026446</v>
+        <v>25.00194735772907</v>
       </c>
       <c r="E82">
-        <v>27.46</v>
+        <v>27.93200000000001</v>
       </c>
       <c r="F82">
-        <v>37.76000000000001</v>
+        <v>38.23200000000001</v>
       </c>
       <c r="G82">
         <v>2.02</v>
@@ -8011,37 +8011,37 @@
         <v>4.95</v>
       </c>
       <c r="M82">
-        <v>5.543168000000001</v>
+        <v>5.612457600000002</v>
       </c>
       <c r="N82">
-        <v>-0.5931680000000012</v>
+        <v>-0.6624576000000015</v>
       </c>
       <c r="O82">
-        <v>-0.08897520000000018</v>
+        <v>-0.09936864000000023</v>
       </c>
       <c r="P82">
-        <v>-0.5041928000000011</v>
+        <v>-0.5630889600000013</v>
       </c>
       <c r="Q82">
-        <v>1.215807199999999</v>
+        <v>1.156911039999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2775559871953117</v>
+        <v>0.289753670731907</v>
       </c>
       <c r="T82">
-        <v>3.020557429089611</v>
+        <v>3.1795341358838</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1339486733939869</v>
+        <v>0.1322949860681353</v>
       </c>
       <c r="W82">
-        <v>0.1271363347457627</v>
+        <v>0.1273790960451978</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.892991155959913</v>
+        <v>0.8819665737875684</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1582302652356725</v>
+        <v>0.1592402652356725</v>
       </c>
       <c r="C83">
-        <v>-11.21005264227094</v>
+        <v>-11.87499015003149</v>
       </c>
       <c r="D83">
-        <v>25.00194735772907</v>
+        <v>24.80900984996852</v>
       </c>
       <c r="E83">
-        <v>27.93200000000001</v>
+        <v>28.40400000000001</v>
       </c>
       <c r="F83">
-        <v>38.23200000000001</v>
+        <v>38.70400000000001</v>
       </c>
       <c r="G83">
         <v>2.02</v>
@@ -8093,37 +8093,37 @@
         <v>4.95</v>
       </c>
       <c r="M83">
-        <v>5.612457600000002</v>
+        <v>5.681747200000002</v>
       </c>
       <c r="N83">
-        <v>-0.6624576000000015</v>
+        <v>-0.7317472000000018</v>
       </c>
       <c r="O83">
-        <v>-0.09936864000000023</v>
+        <v>-0.1097620800000003</v>
       </c>
       <c r="P83">
-        <v>-0.5630889600000013</v>
+        <v>-0.6219851200000015</v>
       </c>
       <c r="Q83">
-        <v>1.156911039999998</v>
+        <v>1.098014879999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.289753670731907</v>
+        <v>0.3033066524392352</v>
       </c>
       <c r="T83">
-        <v>3.1795341358838</v>
+        <v>3.356174921210679</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1322949860681353</v>
+        <v>0.1306816325794994</v>
       </c>
       <c r="W83">
-        <v>0.1273790960451978</v>
+        <v>0.1276159363373295</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8819665737875684</v>
+        <v>0.8712108838633297</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1592402652356725</v>
+        <v>0.1602502652356725</v>
       </c>
       <c r="C84">
-        <v>-11.87499015003149</v>
+        <v>-12.53697270228424</v>
       </c>
       <c r="D84">
-        <v>24.80900984996852</v>
+        <v>24.61902729771577</v>
       </c>
       <c r="E84">
-        <v>28.40400000000001</v>
+        <v>28.87600000000001</v>
       </c>
       <c r="F84">
-        <v>38.70400000000001</v>
+        <v>39.17600000000001</v>
       </c>
       <c r="G84">
         <v>2.02</v>
@@ -8175,37 +8175,37 @@
         <v>4.95</v>
       </c>
       <c r="M84">
-        <v>5.681747200000002</v>
+        <v>5.751036800000002</v>
       </c>
       <c r="N84">
-        <v>-0.7317472000000018</v>
+        <v>-0.8010368000000021</v>
       </c>
       <c r="O84">
-        <v>-0.1097620800000003</v>
+        <v>-0.1201555200000003</v>
       </c>
       <c r="P84">
-        <v>-0.6219851200000015</v>
+        <v>-0.6808812800000018</v>
       </c>
       <c r="Q84">
-        <v>1.098014879999998</v>
+        <v>1.039118719999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3033066524392352</v>
+        <v>0.3184541025827197</v>
       </c>
       <c r="T84">
-        <v>3.356174921210679</v>
+        <v>3.553596975399543</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1306816325794994</v>
+        <v>0.1291071550785416</v>
       </c>
       <c r="W84">
-        <v>0.1276159363373295</v>
+        <v>0.1278470696344701</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8712108838633297</v>
+        <v>0.8607143671902775</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1602502652356725</v>
+        <v>0.1612602652356725</v>
       </c>
       <c r="C85">
-        <v>-12.53697270228424</v>
+        <v>-13.19606766854314</v>
       </c>
       <c r="D85">
-        <v>24.61902729771577</v>
+        <v>24.43193233145687</v>
       </c>
       <c r="E85">
-        <v>28.87600000000001</v>
+        <v>29.348</v>
       </c>
       <c r="F85">
-        <v>39.17600000000001</v>
+        <v>39.648</v>
       </c>
       <c r="G85">
         <v>2.02</v>
@@ -8257,37 +8257,37 @@
         <v>4.95</v>
       </c>
       <c r="M85">
-        <v>5.751036800000002</v>
+        <v>5.820326400000001</v>
       </c>
       <c r="N85">
-        <v>-0.8010368000000021</v>
+        <v>-0.8703264000000006</v>
       </c>
       <c r="O85">
-        <v>-0.1201555200000003</v>
+        <v>-0.1305489600000001</v>
       </c>
       <c r="P85">
-        <v>-0.6808812800000018</v>
+        <v>-0.7397774400000006</v>
       </c>
       <c r="Q85">
-        <v>1.039118719999998</v>
+        <v>0.9802225599999992</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3184541025827197</v>
+        <v>0.3354949839941397</v>
       </c>
       <c r="T85">
-        <v>3.553596975399543</v>
+        <v>3.775696786362015</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1291071550785416</v>
+        <v>0.1275701651371304</v>
       </c>
       <c r="W85">
-        <v>0.1278470696344701</v>
+        <v>0.1280726997578693</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8607143671902775</v>
+        <v>0.8504677675808696</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1612602652356725</v>
+        <v>0.1622702652356725</v>
       </c>
       <c r="C86">
-        <v>-13.19606766854314</v>
+        <v>-13.85234038584051</v>
       </c>
       <c r="D86">
-        <v>24.43193233145687</v>
+        <v>24.24765961415949</v>
       </c>
       <c r="E86">
-        <v>29.348</v>
+        <v>29.82</v>
       </c>
       <c r="F86">
-        <v>39.648</v>
+        <v>40.12</v>
       </c>
       <c r="G86">
         <v>2.02</v>
@@ -8339,37 +8339,37 @@
         <v>4.95</v>
       </c>
       <c r="M86">
-        <v>5.820326400000001</v>
+        <v>5.889616000000001</v>
       </c>
       <c r="N86">
-        <v>-0.8703264000000006</v>
+        <v>-0.9396160000000009</v>
       </c>
       <c r="O86">
-        <v>-0.1305489600000001</v>
+        <v>-0.1409424000000001</v>
       </c>
       <c r="P86">
-        <v>-0.7397774400000006</v>
+        <v>-0.7986736000000008</v>
       </c>
       <c r="Q86">
-        <v>0.9802225599999992</v>
+        <v>0.921326399999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3354949839941395</v>
+        <v>0.3548079829270822</v>
       </c>
       <c r="T86">
-        <v>3.775696786362012</v>
+        <v>4.027409905452813</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1275701651371304</v>
+        <v>0.1260693396649289</v>
       </c>
       <c r="W86">
-        <v>0.1280726997578693</v>
+        <v>0.1282930209371884</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8504677675808696</v>
+        <v>0.8404622644328593</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1622702652356725</v>
+        <v>0.1632802652356725</v>
       </c>
       <c r="C87">
-        <v>-13.85234038584051</v>
+        <v>-14.50585423480113</v>
       </c>
       <c r="D87">
-        <v>24.24765961415949</v>
+        <v>24.06614576519887</v>
       </c>
       <c r="E87">
-        <v>29.82</v>
+        <v>30.292</v>
       </c>
       <c r="F87">
-        <v>40.12</v>
+        <v>40.592</v>
       </c>
       <c r="G87">
         <v>2.02</v>
@@ -8421,37 +8421,37 @@
         <v>4.95</v>
       </c>
       <c r="M87">
-        <v>5.889616000000001</v>
+        <v>5.9589056</v>
       </c>
       <c r="N87">
-        <v>-0.9396160000000009</v>
+        <v>-1.0089056</v>
       </c>
       <c r="O87">
-        <v>-0.1409424000000001</v>
+        <v>-0.15133584</v>
       </c>
       <c r="P87">
-        <v>-0.7986736000000008</v>
+        <v>-0.8575697600000003</v>
       </c>
       <c r="Q87">
-        <v>0.921326399999999</v>
+        <v>0.8624302399999995</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3548079829270822</v>
+        <v>0.376879981707588</v>
       </c>
       <c r="T87">
-        <v>4.027409905452813</v>
+        <v>4.315082041556585</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1260693396649289</v>
+        <v>0.1246034171106856</v>
       </c>
       <c r="W87">
-        <v>0.1282930209371884</v>
+        <v>0.1285082183681514</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8404622644328593</v>
+        <v>0.8306894474045703</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1632802652356725</v>
+        <v>0.1642902652356725</v>
       </c>
       <c r="C88">
-        <v>-14.50585423480113</v>
+        <v>-15.15667071232473</v>
       </c>
       <c r="D88">
-        <v>24.06614576519887</v>
+        <v>23.88732928767527</v>
       </c>
       <c r="E88">
-        <v>30.292</v>
+        <v>30.764</v>
       </c>
       <c r="F88">
-        <v>40.592</v>
+        <v>41.064</v>
       </c>
       <c r="G88">
         <v>2.02</v>
@@ -8503,37 +8503,37 @@
         <v>4.95</v>
       </c>
       <c r="M88">
-        <v>5.9589056</v>
+        <v>6.028195200000001</v>
       </c>
       <c r="N88">
-        <v>-1.0089056</v>
+        <v>-1.078195200000001</v>
       </c>
       <c r="O88">
-        <v>-0.15133584</v>
+        <v>-0.1617292800000001</v>
       </c>
       <c r="P88">
-        <v>-0.8575697600000003</v>
+        <v>-0.9164659200000005</v>
       </c>
       <c r="Q88">
-        <v>0.8624302399999995</v>
+        <v>0.8035340799999993</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.376879981707588</v>
+        <v>0.4023476726081717</v>
       </c>
       <c r="T88">
-        <v>4.315082041556585</v>
+        <v>4.64701142936863</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1246034171106856</v>
+        <v>0.1231711939255052</v>
       </c>
       <c r="W88">
-        <v>0.1285082183681514</v>
+        <v>0.1287184687317358</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8306894474045703</v>
+        <v>0.8211412928367017</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1642902652356725</v>
+        <v>0.1653002652356725</v>
       </c>
       <c r="C89">
-        <v>-15.15667071232473</v>
+        <v>-15.80484950105232</v>
       </c>
       <c r="D89">
-        <v>23.88732928767527</v>
+        <v>23.71115049894768</v>
       </c>
       <c r="E89">
-        <v>30.764</v>
+        <v>31.236</v>
       </c>
       <c r="F89">
-        <v>41.064</v>
+        <v>41.536</v>
       </c>
       <c r="G89">
         <v>2.02</v>
@@ -8585,37 +8585,37 @@
         <v>4.95</v>
       </c>
       <c r="M89">
-        <v>6.028195200000001</v>
+        <v>6.097484800000001</v>
       </c>
       <c r="N89">
-        <v>-1.078195200000001</v>
+        <v>-1.147484800000001</v>
       </c>
       <c r="O89">
-        <v>-0.1617292800000001</v>
+        <v>-0.1721227200000001</v>
       </c>
       <c r="P89">
-        <v>-0.9164659200000005</v>
+        <v>-0.9753620800000007</v>
       </c>
       <c r="Q89">
-        <v>0.8035340799999993</v>
+        <v>0.7446379199999991</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4023476726081717</v>
+        <v>0.4320599786588528</v>
       </c>
       <c r="T89">
-        <v>4.64701142936863</v>
+        <v>5.034262381816017</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1231711939255052</v>
+        <v>0.1217715212672609</v>
       </c>
       <c r="W89">
-        <v>0.1287184687317358</v>
+        <v>0.1289239406779661</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8211412928367017</v>
+        <v>0.8118101417817392</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1653002652356725</v>
+        <v>0.1663102652356725</v>
       </c>
       <c r="C90">
-        <v>-15.80484950105232</v>
+        <v>-16.45044853578069</v>
       </c>
       <c r="D90">
-        <v>23.71115049894768</v>
+        <v>23.53755146421932</v>
       </c>
       <c r="E90">
-        <v>31.236</v>
+        <v>31.708</v>
       </c>
       <c r="F90">
-        <v>41.536</v>
+        <v>42.008</v>
       </c>
       <c r="G90">
         <v>2.02</v>
@@ -8667,37 +8667,37 @@
         <v>4.95</v>
       </c>
       <c r="M90">
-        <v>6.097484800000001</v>
+        <v>6.166774400000001</v>
       </c>
       <c r="N90">
-        <v>-1.147484800000001</v>
+        <v>-1.216774400000001</v>
       </c>
       <c r="O90">
-        <v>-0.1721227200000001</v>
+        <v>-0.1825161600000002</v>
       </c>
       <c r="P90">
-        <v>-0.9753620800000007</v>
+        <v>-1.034258240000001</v>
       </c>
       <c r="Q90">
-        <v>0.7446379199999991</v>
+        <v>0.6857417599999989</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4320599786588528</v>
+        <v>0.4671745221732939</v>
       </c>
       <c r="T90">
-        <v>5.034262381816017</v>
+        <v>5.491922598344745</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1217715212672609</v>
+        <v>0.1204033019271793</v>
       </c>
       <c r="W90">
-        <v>0.1289239406779661</v>
+        <v>0.1291247952770901</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8118101417817392</v>
+        <v>0.8026886795145285</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1663102652356725</v>
+        <v>0.2174163123070406</v>
       </c>
       <c r="C91">
-        <v>-16.45044853578069</v>
+        <v>-23.28511794815657</v>
       </c>
       <c r="D91">
-        <v>23.53755146421932</v>
+        <v>17.17488205184343</v>
       </c>
       <c r="E91">
-        <v>31.708</v>
+        <v>32.18000000000001</v>
       </c>
       <c r="F91">
-        <v>42.008</v>
+        <v>42.48</v>
       </c>
       <c r="G91">
         <v>2.02</v>
@@ -8749,45 +8749,45 @@
         <v>4.95</v>
       </c>
       <c r="M91">
-        <v>6.166774400000001</v>
+        <v>8.529984000000001</v>
       </c>
       <c r="N91">
-        <v>-1.216774400000001</v>
+        <v>-3.579984</v>
       </c>
       <c r="O91">
-        <v>-0.1825161600000002</v>
+        <v>-0.5369976000000001</v>
       </c>
       <c r="P91">
-        <v>-1.034258240000001</v>
+        <v>-3.0429864</v>
       </c>
       <c r="Q91">
-        <v>0.6857417599999989</v>
+        <v>-1.3229864</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4671745221732939</v>
+        <v>0.5242724451043037</v>
       </c>
       <c r="T91">
-        <v>5.491922598344745</v>
+        <v>6.236099943586321</v>
       </c>
       <c r="U91">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1204033019271793</v>
+        <v>0.08704588425957187</v>
       </c>
       <c r="W91">
-        <v>0.1291247952770901</v>
+        <v>0.183321186440678</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8026886795145285</v>
+        <v>0.5803058950638125</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2174163123070406</v>
+        <v>0.2189663123070406</v>
       </c>
       <c r="C92">
-        <v>-23.28511794815657</v>
+        <v>-23.89678217295215</v>
       </c>
       <c r="D92">
-        <v>17.17488205184343</v>
+        <v>17.03521782704786</v>
       </c>
       <c r="E92">
-        <v>32.18000000000001</v>
+        <v>32.652</v>
       </c>
       <c r="F92">
-        <v>42.48</v>
+        <v>42.95200000000001</v>
       </c>
       <c r="G92">
         <v>2.02</v>
@@ -8831,37 +8831,37 @@
         <v>4.95</v>
       </c>
       <c r="M92">
-        <v>8.529984000000001</v>
+        <v>8.624761600000001</v>
       </c>
       <c r="N92">
-        <v>-3.579984</v>
+        <v>-3.674761600000001</v>
       </c>
       <c r="O92">
-        <v>-0.5369976000000001</v>
+        <v>-0.5512142400000001</v>
       </c>
       <c r="P92">
-        <v>-3.0429864</v>
+        <v>-3.123547360000001</v>
       </c>
       <c r="Q92">
-        <v>-1.3229864</v>
+        <v>-1.403547360000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5242724451043037</v>
+        <v>0.5774360501158929</v>
       </c>
       <c r="T92">
-        <v>6.236099943586321</v>
+        <v>6.928999937318135</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08704588425957187</v>
+        <v>0.08608933608089527</v>
       </c>
       <c r="W92">
-        <v>0.183321186440678</v>
+        <v>0.1835132613149562</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5803058950638125</v>
+        <v>0.5739289072059683</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2189663123070406</v>
+        <v>0.2205163123070406</v>
       </c>
       <c r="C93">
-        <v>-23.89678217295215</v>
+        <v>-24.50619325228539</v>
       </c>
       <c r="D93">
-        <v>17.03521782704786</v>
+        <v>16.89780674771461</v>
       </c>
       <c r="E93">
-        <v>32.652</v>
+        <v>33.12400000000001</v>
       </c>
       <c r="F93">
-        <v>42.95200000000001</v>
+        <v>43.42400000000001</v>
       </c>
       <c r="G93">
         <v>2.02</v>
@@ -8913,37 +8913,37 @@
         <v>4.95</v>
       </c>
       <c r="M93">
-        <v>8.624761600000001</v>
+        <v>8.719539200000002</v>
       </c>
       <c r="N93">
-        <v>-3.674761600000001</v>
+        <v>-3.769539200000001</v>
       </c>
       <c r="O93">
-        <v>-0.5512142400000001</v>
+        <v>-0.5654308800000002</v>
       </c>
       <c r="P93">
-        <v>-3.123547360000001</v>
+        <v>-3.204108320000001</v>
       </c>
       <c r="Q93">
-        <v>-1.403547360000001</v>
+        <v>-1.484108320000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5774360501158929</v>
+        <v>0.6438905563803797</v>
       </c>
       <c r="T93">
-        <v>6.928999937318135</v>
+        <v>7.795124929482904</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08608933608089527</v>
+        <v>0.08515358242784203</v>
       </c>
       <c r="W93">
-        <v>0.1835132613149562</v>
+        <v>0.1837011606484893</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5739289072059683</v>
+        <v>0.567690549518947</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2205163123070406</v>
+        <v>0.2220663123070405</v>
       </c>
       <c r="C94">
-        <v>-24.50619325228539</v>
+        <v>-25.11340527347484</v>
       </c>
       <c r="D94">
-        <v>16.89780674771461</v>
+        <v>16.76259472652517</v>
       </c>
       <c r="E94">
-        <v>33.12400000000001</v>
+        <v>33.596</v>
       </c>
       <c r="F94">
-        <v>43.42400000000001</v>
+        <v>43.89600000000001</v>
       </c>
       <c r="G94">
         <v>2.02</v>
@@ -8995,37 +8995,37 @@
         <v>4.95</v>
       </c>
       <c r="M94">
-        <v>8.719539200000002</v>
+        <v>8.814316800000002</v>
       </c>
       <c r="N94">
-        <v>-3.769539200000001</v>
+        <v>-3.864316800000002</v>
       </c>
       <c r="O94">
-        <v>-0.5654308800000002</v>
+        <v>-0.5796475200000003</v>
       </c>
       <c r="P94">
-        <v>-3.204108320000001</v>
+        <v>-3.284669280000001</v>
       </c>
       <c r="Q94">
-        <v>-1.484108320000002</v>
+        <v>-1.564669280000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6438905563803797</v>
+        <v>0.7293320644347199</v>
       </c>
       <c r="T94">
-        <v>7.795124929482904</v>
+        <v>8.908714205123321</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08515358242784203</v>
+        <v>0.08423795250926309</v>
       </c>
       <c r="W94">
-        <v>0.1837011606484893</v>
+        <v>0.18388501913614</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.567690549518947</v>
+        <v>0.5615863500617539</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2220663123070405</v>
+        <v>0.2236163123070405</v>
       </c>
       <c r="C95">
-        <v>-25.11340527347484</v>
+        <v>-25.71847060640869</v>
       </c>
       <c r="D95">
-        <v>16.76259472652517</v>
+        <v>16.62952939359131</v>
       </c>
       <c r="E95">
-        <v>33.596</v>
+        <v>34.068</v>
       </c>
       <c r="F95">
-        <v>43.89600000000001</v>
+        <v>44.368</v>
       </c>
       <c r="G95">
         <v>2.02</v>
@@ -9077,37 +9077,37 @@
         <v>4.95</v>
       </c>
       <c r="M95">
-        <v>8.814316800000002</v>
+        <v>8.909094400000001</v>
       </c>
       <c r="N95">
-        <v>-3.864316800000002</v>
+        <v>-3.959094400000001</v>
       </c>
       <c r="O95">
-        <v>-0.5796475200000003</v>
+        <v>-0.5938641600000001</v>
       </c>
       <c r="P95">
-        <v>-3.284669280000001</v>
+        <v>-3.365230240000001</v>
       </c>
       <c r="Q95">
-        <v>-1.564669280000002</v>
+        <v>-1.645230240000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7293320644347199</v>
+        <v>0.84325407517384</v>
       </c>
       <c r="T95">
-        <v>8.908714205123321</v>
+        <v>10.39349990597721</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08423795250926309</v>
+        <v>0.0833418040783135</v>
       </c>
       <c r="W95">
-        <v>0.18388501913614</v>
+        <v>0.1840649657410747</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5615863500617539</v>
+        <v>0.5556120271887567</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2236163123070405</v>
+        <v>0.2251663123070405</v>
       </c>
       <c r="C96">
-        <v>-25.71847060640869</v>
+        <v>-26.32143997117482</v>
       </c>
       <c r="D96">
-        <v>16.62952939359131</v>
+        <v>16.49856002882519</v>
       </c>
       <c r="E96">
-        <v>34.068</v>
+        <v>34.54000000000001</v>
       </c>
       <c r="F96">
-        <v>44.368</v>
+        <v>44.84</v>
       </c>
       <c r="G96">
         <v>2.02</v>
@@ -9159,37 +9159,37 @@
         <v>4.95</v>
       </c>
       <c r="M96">
-        <v>8.909094400000001</v>
+        <v>9.003872000000001</v>
       </c>
       <c r="N96">
-        <v>-3.959094400000001</v>
+        <v>-4.053872000000001</v>
       </c>
       <c r="O96">
-        <v>-0.5938641600000001</v>
+        <v>-0.6080808000000001</v>
       </c>
       <c r="P96">
-        <v>-3.365230240000001</v>
+        <v>-3.445791200000001</v>
       </c>
       <c r="Q96">
-        <v>-1.645230240000001</v>
+        <v>-1.725791200000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.84325407517384</v>
+        <v>1.002744890208608</v>
       </c>
       <c r="T96">
-        <v>10.39349990597721</v>
+        <v>12.47219988717266</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0833418040783135</v>
+        <v>0.08246452193012073</v>
       </c>
       <c r="W96">
-        <v>0.1840649657410747</v>
+        <v>0.1842411239964317</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5556120271887567</v>
+        <v>0.5497634795341382</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2251663123070405</v>
+        <v>0.2267163123070405</v>
       </c>
       <c r="C97">
-        <v>-26.32143997117482</v>
+        <v>-26.92236250251975</v>
       </c>
       <c r="D97">
-        <v>16.49856002882519</v>
+        <v>16.36963749748026</v>
       </c>
       <c r="E97">
-        <v>34.54000000000001</v>
+        <v>35.012</v>
       </c>
       <c r="F97">
-        <v>44.84</v>
+        <v>45.312</v>
       </c>
       <c r="G97">
         <v>2.02</v>
@@ -9241,37 +9241,37 @@
         <v>4.95</v>
       </c>
       <c r="M97">
-        <v>9.003872000000001</v>
+        <v>9.098649600000002</v>
       </c>
       <c r="N97">
-        <v>-4.053872000000001</v>
+        <v>-4.148649600000001</v>
       </c>
       <c r="O97">
-        <v>-0.6080808000000001</v>
+        <v>-0.6222974400000002</v>
       </c>
       <c r="P97">
-        <v>-3.445791200000001</v>
+        <v>-3.526352160000001</v>
       </c>
       <c r="Q97">
-        <v>-1.725791200000001</v>
+        <v>-1.806352160000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.002744890208608</v>
+        <v>1.241981112760761</v>
       </c>
       <c r="T97">
-        <v>12.47219988717266</v>
+        <v>15.59024985896583</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08246452193012073</v>
+        <v>0.08160551649334863</v>
       </c>
       <c r="W97">
-        <v>0.1842411239964317</v>
+        <v>0.1844136122881356</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5497634795341382</v>
+        <v>0.5440367766223242</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2267163123070405</v>
+        <v>0.2282663123070405</v>
       </c>
       <c r="C98">
-        <v>-26.92236250251974</v>
+        <v>-27.52128581130909</v>
       </c>
       <c r="D98">
-        <v>16.36963749748026</v>
+        <v>16.24271418869091</v>
       </c>
       <c r="E98">
-        <v>35.012</v>
+        <v>35.48399999999999</v>
       </c>
       <c r="F98">
-        <v>45.312</v>
+        <v>45.784</v>
       </c>
       <c r="G98">
         <v>2.02</v>
@@ -9323,37 +9323,37 @@
         <v>4.95</v>
       </c>
       <c r="M98">
-        <v>9.0986496</v>
+        <v>9.1934272</v>
       </c>
       <c r="N98">
-        <v>-4.1486496</v>
+        <v>-4.2434272</v>
       </c>
       <c r="O98">
-        <v>-0.62229744</v>
+        <v>-0.63651408</v>
       </c>
       <c r="P98">
-        <v>-3.52635216</v>
+        <v>-3.60691312</v>
       </c>
       <c r="Q98">
-        <v>-1.80635216</v>
+        <v>-1.88691312</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.241981112760758</v>
+        <v>1.640708150347677</v>
       </c>
       <c r="T98">
-        <v>15.59024985896578</v>
+        <v>20.78699981195438</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08160551649334864</v>
+        <v>0.08076422250888113</v>
       </c>
       <c r="W98">
-        <v>0.1844136122881356</v>
+        <v>0.1845825441202167</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5440367766223243</v>
+        <v>0.5384281500592075</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2282663123070405</v>
+        <v>0.2298163123070406</v>
       </c>
       <c r="C99">
-        <v>-27.52128581130909</v>
+        <v>-28.11825604315069</v>
       </c>
       <c r="D99">
-        <v>16.24271418869091</v>
+        <v>16.11774395684931</v>
       </c>
       <c r="E99">
-        <v>35.48399999999999</v>
+        <v>35.956</v>
       </c>
       <c r="F99">
-        <v>45.784</v>
+        <v>46.256</v>
       </c>
       <c r="G99">
         <v>2.02</v>
@@ -9405,37 +9405,37 @@
         <v>4.95</v>
       </c>
       <c r="M99">
-        <v>9.1934272</v>
+        <v>9.288204800000001</v>
       </c>
       <c r="N99">
-        <v>-4.2434272</v>
+        <v>-4.338204800000001</v>
       </c>
       <c r="O99">
-        <v>-0.63651408</v>
+        <v>-0.6507307200000001</v>
       </c>
       <c r="P99">
-        <v>-3.60691312</v>
+        <v>-3.68747408</v>
       </c>
       <c r="Q99">
-        <v>-1.88691312</v>
+        <v>-1.967474080000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.640708150347677</v>
+        <v>2.438162225521516</v>
       </c>
       <c r="T99">
-        <v>20.78699981195438</v>
+        <v>31.18049971793157</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08076422250888113</v>
+        <v>0.07994009778940274</v>
       </c>
       <c r="W99">
-        <v>0.1845825441202167</v>
+        <v>0.184748028363888</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5384281500592075</v>
+        <v>0.532933985262685</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2298163123070406</v>
+        <v>0.2313663123070405</v>
       </c>
       <c r="C100">
-        <v>-28.11825604315069</v>
+        <v>-28.71331793433207</v>
       </c>
       <c r="D100">
-        <v>16.11774395684931</v>
+        <v>15.99468206566793</v>
       </c>
       <c r="E100">
-        <v>35.956</v>
+        <v>36.428</v>
       </c>
       <c r="F100">
-        <v>46.256</v>
+        <v>46.728</v>
       </c>
       <c r="G100">
         <v>2.02</v>
@@ -9487,37 +9487,37 @@
         <v>4.95</v>
       </c>
       <c r="M100">
-        <v>9.288204800000001</v>
+        <v>9.382982400000001</v>
       </c>
       <c r="N100">
-        <v>-4.338204800000001</v>
+        <v>-4.432982400000001</v>
       </c>
       <c r="O100">
-        <v>-0.6507307200000001</v>
+        <v>-0.6649473600000001</v>
       </c>
       <c r="P100">
-        <v>-3.68747408</v>
+        <v>-3.768035040000001</v>
       </c>
       <c r="Q100">
-        <v>-1.967474080000001</v>
+        <v>-2.048035040000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.438162225521516</v>
+        <v>4.830524451043032</v>
       </c>
       <c r="T100">
-        <v>31.18049971793157</v>
+        <v>62.36099943586315</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07994009778940274</v>
+        <v>0.07913262205415623</v>
       </c>
       <c r="W100">
-        <v>0.184748028363888</v>
+        <v>0.1849101694915254</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.532933985262685</v>
+        <v>0.527550813694375</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2313663123070405</v>
-      </c>
-      <c r="C101">
-        <v>-28.71331793433207</v>
-      </c>
-      <c r="D101">
-        <v>15.99468206566793</v>
-      </c>
-      <c r="E101">
-        <v>36.428</v>
-      </c>
-      <c r="F101">
-        <v>46.728</v>
-      </c>
-      <c r="G101">
-        <v>2.02</v>
-      </c>
-      <c r="H101">
-        <v>36.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6.67</v>
-      </c>
-      <c r="K101">
-        <v>1.72</v>
-      </c>
-      <c r="L101">
-        <v>4.95</v>
-      </c>
-      <c r="M101">
-        <v>9.382982400000001</v>
-      </c>
-      <c r="N101">
-        <v>-4.432982400000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.6649473600000001</v>
-      </c>
-      <c r="P101">
-        <v>-3.768035040000001</v>
-      </c>
-      <c r="Q101">
-        <v>-2.048035040000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.830524451043032</v>
-      </c>
-      <c r="T101">
-        <v>62.36099943586315</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07913262205415623</v>
-      </c>
-      <c r="W101">
-        <v>0.1849101694915254</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.527550813694375</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
